--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C16.0/RANDOMSEARCH_DETAILS_C16.0.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C16.0/RANDOMSEARCH_DETAILS_C16.0.xlsx
@@ -469,17 +469,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>0.9821</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0837</v>
+        <v>1.0859</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2.2626</v>
       </c>
     </row>
     <row r="3">
@@ -498,17 +498,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9845</v>
+        <v>0.9901</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0456</v>
+        <v>0.849</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2.2874</v>
       </c>
     </row>
     <row r="4">
@@ -527,17 +527,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>0.9333</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2821</v>
+        <v>2.2811</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4.6869</v>
       </c>
     </row>
     <row r="5">
@@ -556,17 +556,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9769</v>
+        <v>0.9766</v>
       </c>
       <c r="F5" t="n">
-        <v>1.451</v>
+        <v>1.4637</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3.8853</v>
       </c>
     </row>
     <row r="6">
@@ -585,17 +585,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.9755</v>
+        <v>0.9758</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5004</v>
+        <v>1.4916</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4.0786</v>
       </c>
     </row>
     <row r="7">
@@ -614,17 +614,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8867</v>
+        <v>0.886</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9064</v>
+        <v>2.9126</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>4.9319</v>
       </c>
     </row>
     <row r="8">
@@ -643,17 +643,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8841</v>
+        <v>0.8838</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9496</v>
+        <v>2.9491</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>5.0434</v>
       </c>
     </row>
     <row r="9">
@@ -672,17 +672,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>0.9861</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0416</v>
+        <v>1.0419</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2.463</v>
       </c>
     </row>
     <row r="10">
@@ -701,17 +701,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.8511</v>
+        <v>0.8512</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2188</v>
+        <v>3.2181</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>5.0591</v>
       </c>
     </row>
     <row r="11">
@@ -730,17 +730,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8825</v>
+        <v>0.8821</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9506</v>
+        <v>2.9452</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>5.0357</v>
       </c>
     </row>
     <row r="12">
@@ -759,17 +759,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9222</v>
+        <v>0.8815</v>
       </c>
       <c r="F12" t="n">
-        <v>2.644</v>
+        <v>2.9526</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>5.0537</v>
       </c>
     </row>
     <row r="13">
@@ -788,17 +788,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9659</v>
+        <v>0.9665</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9089</v>
+        <v>1.8927</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5.0588</v>
       </c>
     </row>
     <row r="14">
@@ -817,17 +817,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.8801</v>
+        <v>0.8799</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9648</v>
+        <v>2.9605</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>5.0389</v>
       </c>
     </row>
     <row r="15">
@@ -846,17 +846,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.8821</v>
+        <v>0.8818</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9756</v>
+        <v>2.9693</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>5.0364</v>
       </c>
     </row>
     <row r="16">
@@ -875,17 +875,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9428</v>
+        <v>0.8815</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3428</v>
+        <v>2.9568</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>5.0555</v>
       </c>
     </row>
     <row r="17">
@@ -904,17 +904,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9645</v>
+        <v>0.8811</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9312</v>
+        <v>2.9617</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>5.0561</v>
       </c>
     </row>
     <row r="18">
@@ -933,17 +933,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9736</v>
+        <v>0.9805</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7997</v>
+        <v>1.5942</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4.4788</v>
       </c>
     </row>
     <row r="19">
@@ -962,17 +962,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9779</v>
+        <v>0.9762</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6904</v>
+        <v>1.699</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4.5588</v>
       </c>
     </row>
     <row r="20">
@@ -991,17 +991,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9807</v>
+        <v>0.9806</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6497</v>
+        <v>1.6459</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>4.5799</v>
       </c>
     </row>
     <row r="21">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9751</v>
+        <v>0.9734</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7136</v>
+        <v>1.7493</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>4.6007</v>
       </c>
     </row>
     <row r="22">
@@ -1049,17 +1049,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9558</v>
+        <v>0.9555</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0728</v>
+        <v>2.0783</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>4.5729</v>
       </c>
     </row>
     <row r="23">
@@ -1078,17 +1078,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E23" t="n">
         <v>0.9685</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8468</v>
+        <v>1.8485</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>4.535</v>
       </c>
     </row>
     <row r="24">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.962</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9251</v>
+        <v>1.9213</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>4.5584</v>
       </c>
     </row>
     <row r="25">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9604</v>
+        <v>0.9721</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0405</v>
+        <v>1.6756</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>4.6202</v>
       </c>
     </row>
     <row r="26">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9689</v>
+        <v>0.9557</v>
       </c>
       <c r="F26" t="n">
-        <v>2.0132</v>
+        <v>2.2106</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>4.6298</v>
       </c>
     </row>
     <row r="27">
@@ -1194,17 +1194,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9737</v>
+        <v>0.9745</v>
       </c>
       <c r="F27" t="n">
-        <v>1.8093</v>
+        <v>1.7914</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>4.4037</v>
       </c>
     </row>
     <row r="28">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9758</v>
+        <v>0.974</v>
       </c>
       <c r="F28" t="n">
-        <v>1.7911</v>
+        <v>1.8451</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>4.4621</v>
       </c>
     </row>
     <row r="29">
@@ -1252,17 +1252,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9691</v>
       </c>
       <c r="F29" t="n">
-        <v>1.8597</v>
+        <v>1.8571</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>4.519</v>
       </c>
     </row>
     <row r="30">
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9699</v>
+        <v>0.9722</v>
       </c>
       <c r="F30" t="n">
-        <v>1.8564</v>
+        <v>1.7236</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>4.5816</v>
       </c>
     </row>
     <row r="31">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9796</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>1.6475</v>
+        <v>1.8843</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>4.5662</v>
       </c>
     </row>
     <row r="32">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9728</v>
+        <v>0.9735</v>
       </c>
       <c r="F32" t="n">
-        <v>1.7855</v>
+        <v>1.7825</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>4.4497</v>
       </c>
     </row>
     <row r="33">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9766</v>
+        <v>0.9764</v>
       </c>
       <c r="F33" t="n">
-        <v>1.6299</v>
+        <v>1.6368</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>4.2642</v>
       </c>
     </row>
     <row r="34">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E34" t="n">
         <v>0.9876</v>
       </c>
       <c r="F34" t="n">
-        <v>1.077</v>
+        <v>1.0768</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2.6177</v>
       </c>
     </row>
     <row r="35">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9853</v>
+        <v>0.9855</v>
       </c>
       <c r="F35" t="n">
-        <v>1.1159</v>
+        <v>1.1214</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2.5903</v>
       </c>
     </row>
     <row r="36">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9774</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3345</v>
+        <v>1.3379</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2.7331</v>
       </c>
     </row>
     <row r="37">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9866</v>
+        <v>0.9867</v>
       </c>
       <c r="F37" t="n">
-        <v>1.0975</v>
+        <v>1.0996</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2.8525</v>
       </c>
     </row>
     <row r="38">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9755</v>
+        <v>0.9877</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3871</v>
+        <v>1.0577</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2.794</v>
       </c>
     </row>
     <row r="39">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.973</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>1.4207</v>
+        <v>1.4178</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2.7572</v>
       </c>
     </row>
     <row r="40">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9786</v>
+        <v>0.9785</v>
       </c>
       <c r="F40" t="n">
-        <v>1.2631</v>
+        <v>1.2619</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>3.0132</v>
       </c>
     </row>
     <row r="41">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9888</v>
+        <v>0.9887</v>
       </c>
       <c r="F41" t="n">
-        <v>1.0539</v>
+        <v>1.0584</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>2.5834</v>
       </c>
     </row>
     <row r="42">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9862</v>
+        <v>0.9863</v>
       </c>
       <c r="F42" t="n">
-        <v>1.1176</v>
+        <v>1.1141</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2.6137</v>
       </c>
     </row>
     <row r="43">
@@ -1658,17 +1658,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9819</v>
+        <v>0.9817</v>
       </c>
       <c r="F43" t="n">
-        <v>1.2401</v>
+        <v>1.2416</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2.5749</v>
       </c>
     </row>
     <row r="44">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9875</v>
+        <v>0.9876</v>
       </c>
       <c r="F44" t="n">
-        <v>1.042</v>
+        <v>1.0362</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>2.7353</v>
       </c>
     </row>
     <row r="45">
@@ -1716,17 +1716,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9756</v>
+        <v>0.9877</v>
       </c>
       <c r="F45" t="n">
-        <v>1.3826</v>
+        <v>1.0535</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>2.8059</v>
       </c>
     </row>
     <row r="46">
@@ -1745,17 +1745,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9734</v>
+        <v>0.9736</v>
       </c>
       <c r="F46" t="n">
-        <v>1.4373</v>
+        <v>1.4351</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2.7991</v>
       </c>
     </row>
     <row r="47">
@@ -1774,17 +1774,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E47" t="n">
         <v>0.9705</v>
       </c>
       <c r="F47" t="n">
-        <v>1.4933</v>
+        <v>1.4937</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>2.9024</v>
       </c>
     </row>
     <row r="48">
@@ -1803,17 +1803,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9721</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>1.8784</v>
+        <v>1.8749</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>4.1113</v>
       </c>
     </row>
     <row r="49">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9802</v>
+        <v>0.9801</v>
       </c>
       <c r="F49" t="n">
-        <v>1.2767</v>
+        <v>1.2784</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>2.5999</v>
       </c>
     </row>
     <row r="50">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E50" t="n">
         <v>0.9825</v>
       </c>
       <c r="F50" t="n">
-        <v>1.0922</v>
+        <v>1.0921</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>2.2154</v>
       </c>
     </row>
     <row r="51">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
         <v>0.9693000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>1.3691</v>
+        <v>1.368</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>2.5214</v>
       </c>
     </row>
     <row r="52">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.9836</v>
+        <v>0.9835</v>
       </c>
       <c r="F52" t="n">
-        <v>1.0271</v>
+        <v>1.0278</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>2.506</v>
       </c>
     </row>
     <row r="53">
@@ -1948,17 +1948,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E53" t="n">
         <v>0.9838</v>
       </c>
       <c r="F53" t="n">
-        <v>1.0358</v>
+        <v>1.0386</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>2.3175</v>
       </c>
     </row>
     <row r="54">
@@ -1977,17 +1977,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.982</v>
+        <v>0.9819</v>
       </c>
       <c r="F54" t="n">
-        <v>1.0457</v>
+        <v>1.0448</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>2.3252</v>
       </c>
     </row>
     <row r="55">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9808</v>
+        <v>0.9887</v>
       </c>
       <c r="F55" t="n">
-        <v>1.0914</v>
+        <v>0.8409</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>2.2236</v>
       </c>
     </row>
     <row r="56">
@@ -2035,17 +2035,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9833</v>
+        <v>0.9831</v>
       </c>
       <c r="F56" t="n">
-        <v>1.0713</v>
+        <v>1.0755</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2.2193</v>
       </c>
     </row>
     <row r="57">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9878</v>
+        <v>0.9879</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9179</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>2.2627</v>
       </c>
     </row>
     <row r="58">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.976</v>
+        <v>0.9757</v>
       </c>
       <c r="F58" t="n">
-        <v>1.4915</v>
+        <v>1.4835</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>4.0425</v>
       </c>
     </row>
     <row r="59">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.9754</v>
+        <v>0.9757</v>
       </c>
       <c r="F59" t="n">
-        <v>1.5066</v>
+        <v>1.4929</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>3.9987</v>
       </c>
     </row>
     <row r="60">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9768</v>
       </c>
       <c r="F60" t="n">
-        <v>1.505</v>
+        <v>1.4807</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>4.0184</v>
       </c>
     </row>
     <row r="61">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9759</v>
       </c>
       <c r="F61" t="n">
-        <v>1.4723</v>
+        <v>1.4734</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>4.0224</v>
       </c>
     </row>
     <row r="62">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.9776</v>
+        <v>0.9777</v>
       </c>
       <c r="F62" t="n">
-        <v>1.1576</v>
+        <v>1.1579</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>2.2168</v>
       </c>
     </row>
     <row r="63">
@@ -2238,17 +2238,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.9782</v>
+        <v>0.9786</v>
       </c>
       <c r="F63" t="n">
-        <v>1.1401</v>
+        <v>1.1329</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>2.1952</v>
       </c>
     </row>
     <row r="64">
@@ -2267,17 +2267,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.9784</v>
+        <v>0.9782</v>
       </c>
       <c r="F64" t="n">
-        <v>1.1376</v>
+        <v>1.141</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2.1384</v>
       </c>
     </row>
     <row r="65">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.9785</v>
+        <v>0.9787</v>
       </c>
       <c r="F65" t="n">
-        <v>1.1319</v>
+        <v>1.1321</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>2.1678</v>
       </c>
     </row>
     <row r="66">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9892</v>
+        <v>0.9891</v>
       </c>
       <c r="F66" t="n">
-        <v>0.906</v>
+        <v>0.908</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>2.2811</v>
       </c>
     </row>
     <row r="67">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9818</v>
+        <v>0.9819</v>
       </c>
       <c r="F67" t="n">
-        <v>1.0801</v>
+        <v>1.0771</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>2.1503</v>
       </c>
     </row>
     <row r="68">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9879</v>
+        <v>0.988</v>
       </c>
       <c r="F68" t="n">
-        <v>0.9276</v>
+        <v>0.9233</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>2.246</v>
       </c>
     </row>
     <row r="69">
@@ -2412,17 +2412,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9791</v>
+        <v>0.9796</v>
       </c>
       <c r="F69" t="n">
-        <v>1.6181</v>
+        <v>1.7002</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>4.2609</v>
       </c>
     </row>
     <row r="70">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9776</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F70" t="n">
-        <v>1.7422</v>
+        <v>1.7462</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>4.2849</v>
       </c>
     </row>
     <row r="71">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9821</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>1.65</v>
+        <v>1.6441</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>4.2651</v>
       </c>
     </row>
     <row r="72">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9742</v>
+        <v>0.9744</v>
       </c>
       <c r="F72" t="n">
-        <v>1.7881</v>
+        <v>1.7769</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>4.1949</v>
       </c>
     </row>
     <row r="73">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9828</v>
+        <v>0.9696</v>
       </c>
       <c r="F73" t="n">
-        <v>1.2897</v>
+        <v>1.6207</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>3.2815</v>
       </c>
     </row>
     <row r="74">
@@ -2557,17 +2557,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9776</v>
       </c>
       <c r="F74" t="n">
-        <v>1.4912</v>
+        <v>1.4919</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>3.5201</v>
       </c>
     </row>
     <row r="75">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E75" t="n">
         <v>0.8868</v>
       </c>
       <c r="F75" t="n">
-        <v>2.8751</v>
+        <v>2.8771</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>4.9976</v>
       </c>
     </row>
     <row r="76">
@@ -2615,17 +2615,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>0.8868</v>
       </c>
       <c r="F76" t="n">
-        <v>2.8751</v>
+        <v>2.8771</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>4.9976</v>
       </c>
     </row>
     <row r="77">
@@ -2644,17 +2644,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.9712</v>
+        <v>0.9717</v>
       </c>
       <c r="F77" t="n">
-        <v>1.5916</v>
+        <v>1.5861</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>4.1467</v>
       </c>
     </row>
     <row r="78">
@@ -2673,17 +2673,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.9718</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>1.5811</v>
+        <v>1.5601</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>4.0827</v>
       </c>
     </row>
     <row r="79">
@@ -2702,17 +2702,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.9722</v>
+        <v>0.9738</v>
       </c>
       <c r="F79" t="n">
-        <v>1.5692</v>
+        <v>1.5493</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>4.0928</v>
       </c>
     </row>
     <row r="80">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.9718</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>1.5814</v>
+        <v>1.56</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>4.0844</v>
       </c>
     </row>
     <row r="81">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.9794</v>
+        <v>0.9795</v>
       </c>
       <c r="F81" t="n">
-        <v>1.1234</v>
+        <v>1.1228</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>2.1917</v>
       </c>
     </row>
     <row r="82">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E82" t="n">
         <v>0.9779</v>
       </c>
       <c r="F82" t="n">
-        <v>1.1524</v>
+        <v>1.1526</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>2.1685</v>
       </c>
     </row>
     <row r="83">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.8862</v>
+        <v>0.886</v>
       </c>
       <c r="F83" t="n">
-        <v>2.8839</v>
+        <v>2.8865</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>5.0048</v>
       </c>
     </row>
     <row r="84">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.8864</v>
+        <v>0.8862</v>
       </c>
       <c r="F84" t="n">
-        <v>2.8805</v>
+        <v>2.8828</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>4.988</v>
       </c>
     </row>
     <row r="85">
@@ -2876,17 +2876,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.8868</v>
+        <v>0.8869</v>
       </c>
       <c r="F85" t="n">
-        <v>2.8791</v>
+        <v>2.8814</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>5.0076</v>
       </c>
     </row>
     <row r="86">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E86" t="n">
         <v>0.9744</v>
       </c>
       <c r="F86" t="n">
-        <v>1.7972</v>
+        <v>1.7943</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>4.4708</v>
       </c>
     </row>
     <row r="87">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9765</v>
+        <v>0.9797</v>
       </c>
       <c r="F87" t="n">
-        <v>1.7839</v>
+        <v>1.7236</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>4.3746</v>
       </c>
     </row>
     <row r="88">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9634</v>
+        <v>0.9636</v>
       </c>
       <c r="F88" t="n">
-        <v>2.0533</v>
+        <v>2.0521</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>4.3175</v>
       </c>
     </row>
     <row r="89">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9741</v>
+        <v>0.9734</v>
       </c>
       <c r="F89" t="n">
-        <v>1.7749</v>
+        <v>1.778</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>4.2466</v>
       </c>
     </row>
     <row r="90">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9819</v>
+        <v>0.9817</v>
       </c>
       <c r="F90" t="n">
-        <v>1.2399</v>
+        <v>1.2412</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>2.576</v>
       </c>
     </row>
     <row r="91">
@@ -3050,17 +3050,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9875</v>
+        <v>0.9876</v>
       </c>
       <c r="F91" t="n">
-        <v>1.0417</v>
+        <v>1.0357</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>2.7356</v>
       </c>
     </row>
     <row r="92">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9634</v>
+        <v>0.9636</v>
       </c>
       <c r="F92" t="n">
-        <v>2.0533</v>
+        <v>2.0521</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>4.3175</v>
       </c>
     </row>
     <row r="93">
@@ -3108,17 +3108,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9875</v>
+        <v>0.9876</v>
       </c>
       <c r="F93" t="n">
-        <v>1.0417</v>
+        <v>1.0357</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>2.7356</v>
       </c>
     </row>
     <row r="94">
@@ -3137,17 +3137,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E94" t="n">
         <v>0.9333</v>
       </c>
       <c r="F94" t="n">
-        <v>2.2821</v>
+        <v>2.2811</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>4.6869</v>
       </c>
     </row>
     <row r="95">
@@ -3166,17 +3166,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.9621</v>
+        <v>0.9615</v>
       </c>
       <c r="F95" t="n">
-        <v>2.0502</v>
+        <v>2.0602</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>5.1169</v>
       </c>
     </row>
     <row r="96">
@@ -3195,17 +3195,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.9338</v>
       </c>
       <c r="F96" t="n">
-        <v>1.8221</v>
+        <v>2.2709</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>4.7006</v>
       </c>
     </row>
     <row r="97">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E97" t="n">
         <v>0.9316</v>
       </c>
       <c r="F97" t="n">
-        <v>2.2925</v>
+        <v>2.2918</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>4.694</v>
       </c>
     </row>
     <row r="98">
@@ -3253,17 +3253,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.947</v>
+        <v>0.9689</v>
       </c>
       <c r="F98" t="n">
-        <v>1.871</v>
+        <v>1.5053</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>3.648</v>
       </c>
     </row>
     <row r="99">
@@ -3282,17 +3282,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9757</v>
+        <v>0.9678</v>
       </c>
       <c r="F99" t="n">
-        <v>1.3592</v>
+        <v>1.5328</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>3.6964</v>
       </c>
     </row>
     <row r="100">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9735</v>
+        <v>0.975</v>
       </c>
       <c r="F100" t="n">
-        <v>1.4181</v>
+        <v>1.4188</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>3.7323</v>
       </c>
     </row>
     <row r="101">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9636</v>
+        <v>0.9639</v>
       </c>
       <c r="F101" t="n">
-        <v>1.6134</v>
+        <v>1.6107</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>3.7523</v>
       </c>
     </row>
     <row r="102">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9626</v>
+        <v>0.9729</v>
       </c>
       <c r="F102" t="n">
-        <v>1.6269</v>
+        <v>1.4578</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>3.7876</v>
       </c>
     </row>
     <row r="103">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9676</v>
+        <v>0.9677</v>
       </c>
       <c r="F103" t="n">
-        <v>1.5813</v>
+        <v>1.5807</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>3.654</v>
       </c>
     </row>
     <row r="104">
@@ -3427,17 +3427,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E104" t="n">
         <v>0.9472</v>
       </c>
       <c r="F104" t="n">
-        <v>1.8586</v>
+        <v>1.8581</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>3.6099</v>
       </c>
     </row>
     <row r="105">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9436</v>
+        <v>0.9442</v>
       </c>
       <c r="F105" t="n">
-        <v>1.899</v>
+        <v>1.8895</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>3.5873</v>
       </c>
     </row>
     <row r="106">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9404</v>
+        <v>0.9764</v>
       </c>
       <c r="F106" t="n">
-        <v>1.9634</v>
+        <v>1.368</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>3.6914</v>
       </c>
     </row>
     <row r="107">
@@ -3514,17 +3514,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.964</v>
+        <v>0.9605</v>
       </c>
       <c r="F107" t="n">
-        <v>1.6016</v>
+        <v>1.6608</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>3.7299</v>
       </c>
     </row>
     <row r="108">
@@ -3543,17 +3543,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9692</v>
+        <v>0.9808</v>
       </c>
       <c r="F108" t="n">
-        <v>1.5964</v>
+        <v>1.3578</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>3.5132</v>
       </c>
     </row>
     <row r="109">
@@ -3572,17 +3572,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E109" t="n">
         <v>0.9808</v>
       </c>
       <c r="F109" t="n">
-        <v>1.3012</v>
+        <v>1.303</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>3.4733</v>
       </c>
     </row>
     <row r="110">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9801</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F110" t="n">
-        <v>1.317</v>
+        <v>1.4919</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>3.6017</v>
       </c>
     </row>
     <row r="111">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9749</v>
+        <v>0.9748</v>
       </c>
       <c r="F111" t="n">
-        <v>1.4109</v>
+        <v>1.4108</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>3.5195</v>
       </c>
     </row>
     <row r="112">
@@ -3659,17 +3659,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E112" t="n">
         <v>0.9852</v>
       </c>
       <c r="F112" t="n">
-        <v>1.1339</v>
+        <v>1.1332</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>2.9745</v>
       </c>
     </row>
     <row r="113">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9756</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F113" t="n">
-        <v>1.3976</v>
+        <v>1.4009</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>3.0312</v>
       </c>
     </row>
     <row r="114">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9811</v>
+        <v>0.9749</v>
       </c>
       <c r="F114" t="n">
-        <v>1.2901</v>
+        <v>1.4344</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>3.4732</v>
       </c>
     </row>
     <row r="115">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9751</v>
       </c>
       <c r="F115" t="n">
-        <v>1.4072</v>
+        <v>1.41</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>3.5086</v>
       </c>
     </row>
     <row r="116">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9872</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="F116" t="n">
-        <v>0.9171</v>
+        <v>0.9113</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>2.2819</v>
       </c>
     </row>
     <row r="117">
@@ -3804,17 +3804,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.9846</v>
       </c>
       <c r="F117" t="n">
-        <v>0.9977</v>
+        <v>0.9919</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>2.2941</v>
       </c>
     </row>
     <row r="118">
@@ -3833,17 +3833,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9436</v>
+        <v>0.9442</v>
       </c>
       <c r="F118" t="n">
-        <v>1.899</v>
+        <v>1.8895</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>3.5873</v>
       </c>
     </row>
     <row r="119">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9756</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F119" t="n">
-        <v>1.3976</v>
+        <v>1.4009</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>3.0312</v>
       </c>
     </row>
     <row r="120">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9528</v>
+        <v>0.9534</v>
       </c>
       <c r="F120" t="n">
-        <v>1.9553</v>
+        <v>1.9436</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>4.5918</v>
       </c>
     </row>
     <row r="121">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9528</v>
+        <v>0.9534</v>
       </c>
       <c r="F121" t="n">
-        <v>1.9553</v>
+        <v>1.9436</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>4.5918</v>
       </c>
     </row>
     <row r="122">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.919</v>
+        <v>0.9186</v>
       </c>
       <c r="F122" t="n">
-        <v>2.3847</v>
+        <v>2.3893</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>4.1805</v>
       </c>
     </row>
     <row r="123">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9755</v>
+        <v>0.9752</v>
       </c>
       <c r="F123" t="n">
-        <v>1.3974</v>
+        <v>1.3999</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>3.0345</v>
       </c>
     </row>
     <row r="124">
@@ -4007,17 +4007,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9806</v>
+        <v>0.9809</v>
       </c>
       <c r="F124" t="n">
-        <v>1.2983</v>
+        <v>1.2889</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>3.2645</v>
       </c>
     </row>
     <row r="125">
@@ -4036,17 +4036,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9326</v>
+        <v>0.9328</v>
       </c>
       <c r="F125" t="n">
-        <v>2.3007</v>
+        <v>2.3012</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>4.693</v>
       </c>
     </row>
     <row r="126">
@@ -4065,17 +4065,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.8751</v>
+        <v>0.8752</v>
       </c>
       <c r="F126" t="n">
-        <v>2.9808</v>
+        <v>2.9793</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>4.8756</v>
       </c>
     </row>
     <row r="127">
@@ -4094,17 +4094,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.975</v>
+        <v>0.9752</v>
       </c>
       <c r="F127" t="n">
-        <v>1.2674</v>
+        <v>1.2661</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>2.9362</v>
       </c>
     </row>
     <row r="128">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.873</v>
+        <v>0.8732</v>
       </c>
       <c r="F128" t="n">
-        <v>2.9917</v>
+        <v>2.9899</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>4.8788</v>
       </c>
     </row>
     <row r="129">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.8736</v>
+        <v>0.8737</v>
       </c>
       <c r="F129" t="n">
-        <v>2.9905</v>
+        <v>2.9887</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>4.8638</v>
       </c>
     </row>
     <row r="130">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E130" t="n">
         <v>0.8741</v>
       </c>
       <c r="F130" t="n">
-        <v>2.9883</v>
+        <v>2.9871</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>4.8654</v>
       </c>
     </row>
     <row r="131">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E131" t="n">
         <v>0.8744</v>
       </c>
       <c r="F131" t="n">
-        <v>2.9844</v>
+        <v>2.9833</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>4.8688</v>
       </c>
     </row>
     <row r="132">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.8746</v>
+        <v>0.8749</v>
       </c>
       <c r="F132" t="n">
-        <v>2.982</v>
+        <v>2.9797</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>4.8711</v>
       </c>
     </row>
     <row r="133">
@@ -4268,17 +4268,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.8749</v>
+        <v>0.8751</v>
       </c>
       <c r="F133" t="n">
-        <v>2.9823</v>
+        <v>2.9802</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>4.8753</v>
       </c>
     </row>
     <row r="134">
@@ -4297,17 +4297,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.8752</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="F134" t="n">
-        <v>2.9735</v>
+        <v>2.9717</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>4.8802</v>
       </c>
     </row>
     <row r="135">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.8734</v>
+        <v>0.8736</v>
       </c>
       <c r="F135" t="n">
-        <v>2.9891</v>
+        <v>2.9873</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>4.8769</v>
       </c>
     </row>
     <row r="136">
@@ -4355,17 +4355,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.8743</v>
+        <v>0.8744</v>
       </c>
       <c r="F136" t="n">
-        <v>2.9856</v>
+        <v>2.9842</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>4.866</v>
       </c>
     </row>
     <row r="137">
@@ -4384,17 +4384,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9389</v>
+        <v>0.9742</v>
       </c>
       <c r="F137" t="n">
-        <v>2.312</v>
+        <v>1.6944</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>4.5232</v>
       </c>
     </row>
     <row r="138">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9692</v>
+        <v>0.9752</v>
       </c>
       <c r="F138" t="n">
-        <v>1.804</v>
+        <v>1.6785</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>4.3728</v>
       </c>
     </row>
     <row r="139">
@@ -4442,17 +4442,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.959</v>
+        <v>0.9585</v>
       </c>
       <c r="F139" t="n">
-        <v>1.9374</v>
+        <v>1.9407</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>4.5518</v>
       </c>
     </row>
     <row r="140">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.9761</v>
+        <v>0.976</v>
       </c>
       <c r="F140" t="n">
-        <v>1.4065</v>
+        <v>1.4086</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>2.9874</v>
       </c>
     </row>
     <row r="141">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9883</v>
+        <v>0.9872</v>
       </c>
       <c r="F141" t="n">
-        <v>1.1029</v>
+        <v>1.1503</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>3.0109</v>
       </c>
     </row>
     <row r="142">
@@ -4529,17 +4529,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9692</v>
+        <v>0.9752</v>
       </c>
       <c r="F142" t="n">
-        <v>1.804</v>
+        <v>1.6785</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>4.3728</v>
       </c>
     </row>
     <row r="143">
@@ -4558,17 +4558,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9715</v>
+        <v>0.9627</v>
       </c>
       <c r="F143" t="n">
-        <v>1.6894</v>
+        <v>1.8719</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>4.5242</v>
       </c>
     </row>
     <row r="144">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9641</v>
+        <v>0.9636</v>
       </c>
       <c r="F144" t="n">
-        <v>1.8352</v>
+        <v>1.8371</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>4.4542</v>
       </c>
     </row>
     <row r="145">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9883</v>
+        <v>0.9872</v>
       </c>
       <c r="F145" t="n">
-        <v>1.1029</v>
+        <v>1.1503</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>3.0109</v>
       </c>
     </row>
     <row r="146">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9631</v>
       </c>
       <c r="F146" t="n">
-        <v>1.5098</v>
+        <v>1.5096</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>2.8832</v>
       </c>
     </row>
     <row r="147">
@@ -4674,17 +4674,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9633</v>
       </c>
       <c r="F147" t="n">
-        <v>1.5168</v>
+        <v>1.5138</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>2.8926</v>
       </c>
     </row>
     <row r="148">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.9761</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F148" t="n">
-        <v>1.2424</v>
+        <v>1.2381</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>2.8936</v>
       </c>
     </row>
     <row r="149">
@@ -4732,17 +4732,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.9785</v>
+        <v>0.9843</v>
       </c>
       <c r="F149" t="n">
-        <v>1.1977</v>
+        <v>1.0387</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>2.9537</v>
       </c>
     </row>
     <row r="150">
@@ -4761,17 +4761,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.9625</v>
+        <v>0.9626</v>
       </c>
       <c r="F150" t="n">
-        <v>1.5229</v>
+        <v>1.5198</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>2.9247</v>
       </c>
     </row>
     <row r="151">
@@ -4790,17 +4790,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E151" t="n">
         <v>0.9631</v>
       </c>
       <c r="F151" t="n">
-        <v>1.5126</v>
+        <v>1.509</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>2.924</v>
       </c>
     </row>
     <row r="152">
@@ -4819,17 +4819,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E152" t="n">
         <v>0.963</v>
       </c>
       <c r="F152" t="n">
-        <v>1.5169</v>
+        <v>1.5154</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>2.9225</v>
       </c>
     </row>
     <row r="153">
@@ -4848,17 +4848,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.9631</v>
+        <v>0.963</v>
       </c>
       <c r="F153" t="n">
-        <v>1.5116</v>
+        <v>1.5135</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>2.8959</v>
       </c>
     </row>
     <row r="154">
@@ -4877,17 +4877,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.9841</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="F154" t="n">
-        <v>1.0415</v>
+        <v>1.4937</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>2.9245</v>
       </c>
     </row>
     <row r="155">
@@ -4906,17 +4906,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.9862</v>
+        <v>0.9771</v>
       </c>
       <c r="F155" t="n">
-        <v>0.9339</v>
+        <v>1.1705</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>2.3212</v>
       </c>
     </row>
     <row r="156">
@@ -4935,17 +4935,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.9766</v>
+        <v>0.9767</v>
       </c>
       <c r="F156" t="n">
-        <v>1.1753</v>
+        <v>1.1714</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>2.276</v>
       </c>
     </row>
     <row r="157">
@@ -4964,17 +4964,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.9745</v>
+        <v>0.9755</v>
       </c>
       <c r="F157" t="n">
-        <v>1.2253</v>
+        <v>1.2026</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>2.3332</v>
       </c>
     </row>
     <row r="158">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.99</v>
+        <v>0.9898</v>
       </c>
       <c r="F158" t="n">
-        <v>0.8223</v>
+        <v>0.8255</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>2.0644</v>
       </c>
     </row>
     <row r="159">
@@ -5022,17 +5022,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.9072</v>
+        <v>0.9073</v>
       </c>
       <c r="F159" t="n">
-        <v>2.6024</v>
+        <v>2.6007</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>4.8816</v>
       </c>
     </row>
     <row r="160">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E160" t="n">
         <v>0.9520999999999999</v>
       </c>
       <c r="F160" t="n">
-        <v>1.7763</v>
+        <v>1.7756</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>3.3058</v>
       </c>
     </row>
     <row r="161">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.9515</v>
+        <v>0.9516</v>
       </c>
       <c r="F161" t="n">
-        <v>1.7873</v>
+        <v>1.7854</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>3.3142</v>
       </c>
     </row>
     <row r="162">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.907</v>
       </c>
       <c r="F162" t="n">
-        <v>2.6088</v>
+        <v>2.6082</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>4.8839</v>
       </c>
     </row>
     <row r="163">
@@ -5138,17 +5138,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9567</v>
+        <v>0.9558</v>
       </c>
       <c r="F163" t="n">
-        <v>2.1918</v>
+        <v>2.2022</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>4.3172</v>
       </c>
     </row>
     <row r="164">
@@ -5167,17 +5167,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E164" t="n">
         <v>0.9758</v>
       </c>
       <c r="F164" t="n">
-        <v>1.4097</v>
+        <v>1.4116</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>2.9902</v>
       </c>
     </row>
     <row r="165">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9326</v>
+        <v>0.9328</v>
       </c>
       <c r="F165" t="n">
-        <v>2.3007</v>
+        <v>2.3012</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>4.693</v>
       </c>
     </row>
     <row r="166">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.8192</v>
+        <v>0.8195</v>
       </c>
       <c r="F166" t="n">
-        <v>3.4258</v>
+        <v>3.425</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>5.1211</v>
       </c>
     </row>
     <row r="167">
@@ -5254,17 +5254,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9761</v>
+        <v>0.9779</v>
       </c>
       <c r="F167" t="n">
-        <v>1.7217</v>
+        <v>1.7255</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>4.4806</v>
       </c>
     </row>
     <row r="168">
@@ -5283,17 +5283,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E168" t="n">
         <v>0.9862</v>
       </c>
       <c r="F168" t="n">
-        <v>1.1088</v>
+        <v>1.1082</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>2.8764</v>
       </c>
     </row>
     <row r="169">
@@ -5312,17 +5312,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9875</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="F169" t="n">
-        <v>0.9187</v>
+        <v>0.9214</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="170">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E170" t="n">
         <v>0.9758</v>
       </c>
       <c r="F170" t="n">
-        <v>1.5966</v>
+        <v>1.6012</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>3.4639</v>
       </c>
     </row>
     <row r="171">
@@ -5370,17 +5370,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9817</v>
+        <v>0.9816</v>
       </c>
       <c r="F171" t="n">
-        <v>1.2168</v>
+        <v>1.2192</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>2.5267</v>
       </c>
     </row>
     <row r="172">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E172" t="n">
         <v>0.9725</v>
       </c>
       <c r="F172" t="n">
-        <v>1.7617</v>
+        <v>1.7668</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>4.3031</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C16.0/RANDOMSEARCH_DETAILS_C16.0.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C16.0/RANDOMSEARCH_DETAILS_C16.0.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,10 +444,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>RMSEC</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>RMSECV</t>
         </is>
@@ -476,9 +481,12 @@
         <v>0.9821</v>
       </c>
       <c r="F2" t="n">
+        <v>1.1863</v>
+      </c>
+      <c r="G2" t="n">
         <v>1.0859</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>2.2626</v>
       </c>
     </row>
@@ -505,9 +513,12 @@
         <v>0.9901</v>
       </c>
       <c r="F3" t="n">
+        <v>1.1904</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.849</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>2.2874</v>
       </c>
     </row>
@@ -534,9 +545,12 @@
         <v>0.9333</v>
       </c>
       <c r="F4" t="n">
+        <v>1.7993</v>
+      </c>
+      <c r="G4" t="n">
         <v>2.2811</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>4.6869</v>
       </c>
     </row>
@@ -563,9 +577,12 @@
         <v>0.9766</v>
       </c>
       <c r="F5" t="n">
+        <v>1.5493</v>
+      </c>
+      <c r="G5" t="n">
         <v>1.4637</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>3.8853</v>
       </c>
     </row>
@@ -592,9 +609,12 @@
         <v>0.9758</v>
       </c>
       <c r="F6" t="n">
+        <v>1.6053</v>
+      </c>
+      <c r="G6" t="n">
         <v>1.4916</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>4.0786</v>
       </c>
     </row>
@@ -621,9 +641,12 @@
         <v>0.886</v>
       </c>
       <c r="F7" t="n">
+        <v>1.8851</v>
+      </c>
+      <c r="G7" t="n">
         <v>2.9126</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>4.9319</v>
       </c>
     </row>
@@ -650,9 +673,12 @@
         <v>0.8838</v>
       </c>
       <c r="F8" t="n">
+        <v>1.9255</v>
+      </c>
+      <c r="G8" t="n">
         <v>2.9491</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>5.0434</v>
       </c>
     </row>
@@ -679,9 +705,12 @@
         <v>0.9861</v>
       </c>
       <c r="F9" t="n">
+        <v>1.2207</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.0419</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>2.463</v>
       </c>
     </row>
@@ -708,9 +737,12 @@
         <v>0.8512</v>
       </c>
       <c r="F10" t="n">
+        <v>1.9313</v>
+      </c>
+      <c r="G10" t="n">
         <v>3.2181</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>5.0591</v>
       </c>
     </row>
@@ -737,9 +769,12 @@
         <v>0.8821</v>
       </c>
       <c r="F11" t="n">
+        <v>1.9227</v>
+      </c>
+      <c r="G11" t="n">
         <v>2.9452</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>5.0357</v>
       </c>
     </row>
@@ -766,9 +801,12 @@
         <v>0.8815</v>
       </c>
       <c r="F12" t="n">
+        <v>1.9293</v>
+      </c>
+      <c r="G12" t="n">
         <v>2.9526</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>5.0537</v>
       </c>
     </row>
@@ -795,9 +833,12 @@
         <v>0.9665</v>
       </c>
       <c r="F13" t="n">
+        <v>1.9312</v>
+      </c>
+      <c r="G13" t="n">
         <v>1.8927</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>5.0588</v>
       </c>
     </row>
@@ -824,9 +865,12 @@
         <v>0.8799</v>
       </c>
       <c r="F14" t="n">
+        <v>1.9239</v>
+      </c>
+      <c r="G14" t="n">
         <v>2.9605</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>5.0389</v>
       </c>
     </row>
@@ -853,9 +897,12 @@
         <v>0.8818</v>
       </c>
       <c r="F15" t="n">
+        <v>1.923</v>
+      </c>
+      <c r="G15" t="n">
         <v>2.9693</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>5.0364</v>
       </c>
     </row>
@@ -882,9 +929,12 @@
         <v>0.8815</v>
       </c>
       <c r="F16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G16" t="n">
         <v>2.9568</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>5.0555</v>
       </c>
     </row>
@@ -911,9 +961,12 @@
         <v>0.8811</v>
       </c>
       <c r="F17" t="n">
+        <v>1.9302</v>
+      </c>
+      <c r="G17" t="n">
         <v>2.9617</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>5.0561</v>
       </c>
     </row>
@@ -940,9 +993,12 @@
         <v>0.9805</v>
       </c>
       <c r="F18" t="n">
+        <v>1.7299</v>
+      </c>
+      <c r="G18" t="n">
         <v>1.5942</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>4.4788</v>
       </c>
     </row>
@@ -969,9 +1025,12 @@
         <v>0.9762</v>
       </c>
       <c r="F19" t="n">
+        <v>1.7562</v>
+      </c>
+      <c r="G19" t="n">
         <v>1.699</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>4.5588</v>
       </c>
     </row>
@@ -998,9 +1057,12 @@
         <v>0.9806</v>
       </c>
       <c r="F20" t="n">
+        <v>1.7632</v>
+      </c>
+      <c r="G20" t="n">
         <v>1.6459</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>4.5799</v>
       </c>
     </row>
@@ -1027,9 +1089,12 @@
         <v>0.9734</v>
       </c>
       <c r="F21" t="n">
+        <v>1.7702</v>
+      </c>
+      <c r="G21" t="n">
         <v>1.7493</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>4.6007</v>
       </c>
     </row>
@@ -1056,9 +1121,12 @@
         <v>0.9555</v>
       </c>
       <c r="F22" t="n">
+        <v>1.7609</v>
+      </c>
+      <c r="G22" t="n">
         <v>2.0783</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>4.5729</v>
       </c>
     </row>
@@ -1085,9 +1153,12 @@
         <v>0.9685</v>
       </c>
       <c r="F23" t="n">
+        <v>1.7484</v>
+      </c>
+      <c r="G23" t="n">
         <v>1.8485</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>4.535</v>
       </c>
     </row>
@@ -1114,9 +1185,12 @@
         <v>0.9622000000000001</v>
       </c>
       <c r="F24" t="n">
+        <v>1.7561</v>
+      </c>
+      <c r="G24" t="n">
         <v>1.9213</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>4.5584</v>
       </c>
     </row>
@@ -1143,9 +1217,12 @@
         <v>0.9721</v>
       </c>
       <c r="F25" t="n">
+        <v>1.7767</v>
+      </c>
+      <c r="G25" t="n">
         <v>1.6756</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>4.6202</v>
       </c>
     </row>
@@ -1172,9 +1249,12 @@
         <v>0.9557</v>
       </c>
       <c r="F26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G26" t="n">
         <v>2.2106</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>4.6298</v>
       </c>
     </row>
@@ -1201,9 +1281,12 @@
         <v>0.9745</v>
       </c>
       <c r="F27" t="n">
+        <v>1.7056</v>
+      </c>
+      <c r="G27" t="n">
         <v>1.7914</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>4.4037</v>
       </c>
     </row>
@@ -1230,9 +1313,12 @@
         <v>0.974</v>
       </c>
       <c r="F28" t="n">
+        <v>1.7245</v>
+      </c>
+      <c r="G28" t="n">
         <v>1.8451</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>4.4621</v>
       </c>
     </row>
@@ -1259,9 +1345,12 @@
         <v>0.9691</v>
       </c>
       <c r="F29" t="n">
+        <v>1.7431</v>
+      </c>
+      <c r="G29" t="n">
         <v>1.8571</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>4.519</v>
       </c>
     </row>
@@ -1288,9 +1377,12 @@
         <v>0.9722</v>
       </c>
       <c r="F30" t="n">
+        <v>1.7638</v>
+      </c>
+      <c r="G30" t="n">
         <v>1.7236</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>4.5816</v>
       </c>
     </row>
@@ -1317,9 +1409,12 @@
         <v>0.9703000000000001</v>
       </c>
       <c r="F31" t="n">
+        <v>1.7587</v>
+      </c>
+      <c r="G31" t="n">
         <v>1.8843</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>4.5662</v>
       </c>
     </row>
@@ -1346,9 +1441,12 @@
         <v>0.9735</v>
       </c>
       <c r="F32" t="n">
+        <v>1.7205</v>
+      </c>
+      <c r="G32" t="n">
         <v>1.7825</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>4.4497</v>
       </c>
     </row>
@@ -1375,9 +1473,12 @@
         <v>0.9764</v>
       </c>
       <c r="F33" t="n">
+        <v>1.6616</v>
+      </c>
+      <c r="G33" t="n">
         <v>1.6368</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>4.2642</v>
       </c>
     </row>
@@ -1404,9 +1505,12 @@
         <v>0.9876</v>
       </c>
       <c r="F34" t="n">
+        <v>1.2493</v>
+      </c>
+      <c r="G34" t="n">
         <v>1.0768</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>2.6177</v>
       </c>
     </row>
@@ -1433,9 +1537,12 @@
         <v>0.9855</v>
       </c>
       <c r="F35" t="n">
+        <v>1.2441</v>
+      </c>
+      <c r="G35" t="n">
         <v>1.1214</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>2.5903</v>
       </c>
     </row>
@@ -1462,9 +1569,12 @@
         <v>0.9772999999999999</v>
       </c>
       <c r="F36" t="n">
+        <v>1.2718</v>
+      </c>
+      <c r="G36" t="n">
         <v>1.3379</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>2.7331</v>
       </c>
     </row>
@@ -1491,9 +1601,12 @@
         <v>0.9867</v>
       </c>
       <c r="F37" t="n">
+        <v>1.2961</v>
+      </c>
+      <c r="G37" t="n">
         <v>1.0996</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>2.8525</v>
       </c>
     </row>
@@ -1520,9 +1633,12 @@
         <v>0.9877</v>
       </c>
       <c r="F38" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="G38" t="n">
         <v>1.0577</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>2.794</v>
       </c>
     </row>
@@ -1549,9 +1665,12 @@
         <v>0.9733000000000001</v>
       </c>
       <c r="F39" t="n">
+        <v>1.2766</v>
+      </c>
+      <c r="G39" t="n">
         <v>1.4178</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>2.7572</v>
       </c>
     </row>
@@ -1578,9 +1697,12 @@
         <v>0.9785</v>
       </c>
       <c r="F40" t="n">
+        <v>1.3304</v>
+      </c>
+      <c r="G40" t="n">
         <v>1.2619</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>3.0132</v>
       </c>
     </row>
@@ -1607,9 +1729,12 @@
         <v>0.9887</v>
       </c>
       <c r="F41" t="n">
+        <v>1.2428</v>
+      </c>
+      <c r="G41" t="n">
         <v>1.0584</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>2.5834</v>
       </c>
     </row>
@@ -1636,9 +1761,12 @@
         <v>0.9863</v>
       </c>
       <c r="F42" t="n">
+        <v>1.2486</v>
+      </c>
+      <c r="G42" t="n">
         <v>1.1141</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>2.6137</v>
       </c>
     </row>
@@ -1665,9 +1793,12 @@
         <v>0.9817</v>
       </c>
       <c r="F43" t="n">
+        <v>1.2413</v>
+      </c>
+      <c r="G43" t="n">
         <v>1.2416</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>2.5749</v>
       </c>
     </row>
@@ -1694,9 +1825,12 @@
         <v>0.9876</v>
       </c>
       <c r="F44" t="n">
+        <v>1.2722</v>
+      </c>
+      <c r="G44" t="n">
         <v>1.0362</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>2.7353</v>
       </c>
     </row>
@@ -1723,9 +1857,12 @@
         <v>0.9877</v>
       </c>
       <c r="F45" t="n">
+        <v>1.2865</v>
+      </c>
+      <c r="G45" t="n">
         <v>1.0535</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>2.8059</v>
       </c>
     </row>
@@ -1752,9 +1889,12 @@
         <v>0.9736</v>
       </c>
       <c r="F46" t="n">
+        <v>1.2851</v>
+      </c>
+      <c r="G46" t="n">
         <v>1.4351</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>2.7991</v>
       </c>
     </row>
@@ -1781,9 +1921,12 @@
         <v>0.9705</v>
       </c>
       <c r="F47" t="n">
+        <v>1.3065</v>
+      </c>
+      <c r="G47" t="n">
         <v>1.4937</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>2.9024</v>
       </c>
     </row>
@@ -1810,9 +1953,12 @@
         <v>0.9723000000000001</v>
       </c>
       <c r="F48" t="n">
+        <v>1.615</v>
+      </c>
+      <c r="G48" t="n">
         <v>1.8749</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>4.1113</v>
       </c>
     </row>
@@ -1839,9 +1985,12 @@
         <v>0.9801</v>
       </c>
       <c r="F49" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="G49" t="n">
         <v>1.2784</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>2.5999</v>
       </c>
     </row>
@@ -1861,16 +2010,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
         <v>0.9825</v>
       </c>
       <c r="F50" t="n">
+        <v>1.1786</v>
+      </c>
+      <c r="G50" t="n">
         <v>1.0921</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>2.2154</v>
       </c>
     </row>
@@ -1897,9 +2049,12 @@
         <v>0.9693000000000001</v>
       </c>
       <c r="F51" t="n">
+        <v>1.2313</v>
+      </c>
+      <c r="G51" t="n">
         <v>1.368</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>2.5214</v>
       </c>
     </row>
@@ -1926,9 +2081,12 @@
         <v>0.9835</v>
       </c>
       <c r="F52" t="n">
+        <v>1.2285</v>
+      </c>
+      <c r="G52" t="n">
         <v>1.0278</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>2.506</v>
       </c>
     </row>
@@ -1955,9 +2113,12 @@
         <v>0.9838</v>
       </c>
       <c r="F53" t="n">
+        <v>1.1954</v>
+      </c>
+      <c r="G53" t="n">
         <v>1.0386</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>2.3175</v>
       </c>
     </row>
@@ -1984,9 +2145,12 @@
         <v>0.9819</v>
       </c>
       <c r="F54" t="n">
+        <v>1.1967</v>
+      </c>
+      <c r="G54" t="n">
         <v>1.0448</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>2.3252</v>
       </c>
     </row>
@@ -2013,9 +2177,12 @@
         <v>0.9887</v>
       </c>
       <c r="F55" t="n">
+        <v>1.1799</v>
+      </c>
+      <c r="G55" t="n">
         <v>0.8409</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>2.2236</v>
       </c>
     </row>
@@ -2042,9 +2209,12 @@
         <v>0.9831</v>
       </c>
       <c r="F56" t="n">
+        <v>1.1792</v>
+      </c>
+      <c r="G56" t="n">
         <v>1.0755</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>2.2193</v>
       </c>
     </row>
@@ -2071,9 +2241,12 @@
         <v>0.9879</v>
       </c>
       <c r="F57" t="n">
+        <v>1.1863</v>
+      </c>
+      <c r="G57" t="n">
         <v>0.9189000000000001</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>2.2627</v>
       </c>
     </row>
@@ -2100,9 +2273,12 @@
         <v>0.9757</v>
       </c>
       <c r="F58" t="n">
+        <v>1.5946</v>
+      </c>
+      <c r="G58" t="n">
         <v>1.4835</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>4.0425</v>
       </c>
     </row>
@@ -2129,9 +2305,12 @@
         <v>0.9757</v>
       </c>
       <c r="F59" t="n">
+        <v>1.5818</v>
+      </c>
+      <c r="G59" t="n">
         <v>1.4929</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>3.9987</v>
       </c>
     </row>
@@ -2158,9 +2337,12 @@
         <v>0.9768</v>
       </c>
       <c r="F60" t="n">
+        <v>1.5876</v>
+      </c>
+      <c r="G60" t="n">
         <v>1.4807</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>4.0184</v>
       </c>
     </row>
@@ -2187,9 +2369,12 @@
         <v>0.9759</v>
       </c>
       <c r="F61" t="n">
+        <v>1.5887</v>
+      </c>
+      <c r="G61" t="n">
         <v>1.4734</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>4.0224</v>
       </c>
     </row>
@@ -2216,9 +2401,12 @@
         <v>0.9777</v>
       </c>
       <c r="F62" t="n">
+        <v>1.1788</v>
+      </c>
+      <c r="G62" t="n">
         <v>1.1579</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>2.2168</v>
       </c>
     </row>
@@ -2245,9 +2433,12 @@
         <v>0.9786</v>
       </c>
       <c r="F63" t="n">
+        <v>1.1753</v>
+      </c>
+      <c r="G63" t="n">
         <v>1.1329</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>2.1952</v>
       </c>
     </row>
@@ -2274,9 +2465,12 @@
         <v>0.9782</v>
       </c>
       <c r="F64" t="n">
+        <v>1.1664</v>
+      </c>
+      <c r="G64" t="n">
         <v>1.141</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>2.1384</v>
       </c>
     </row>
@@ -2303,9 +2497,12 @@
         <v>0.9787</v>
       </c>
       <c r="F65" t="n">
+        <v>1.171</v>
+      </c>
+      <c r="G65" t="n">
         <v>1.1321</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>2.1678</v>
       </c>
     </row>
@@ -2332,9 +2529,12 @@
         <v>0.9891</v>
       </c>
       <c r="F66" t="n">
+        <v>1.1893</v>
+      </c>
+      <c r="G66" t="n">
         <v>0.908</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>2.2811</v>
       </c>
     </row>
@@ -2361,9 +2561,12 @@
         <v>0.9819</v>
       </c>
       <c r="F67" t="n">
+        <v>1.1682</v>
+      </c>
+      <c r="G67" t="n">
         <v>1.0771</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>2.1503</v>
       </c>
     </row>
@@ -2390,9 +2593,12 @@
         <v>0.988</v>
       </c>
       <c r="F68" t="n">
+        <v>1.1836</v>
+      </c>
+      <c r="G68" t="n">
         <v>0.9233</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>2.246</v>
       </c>
     </row>
@@ -2419,9 +2625,12 @@
         <v>0.9796</v>
       </c>
       <c r="F69" t="n">
+        <v>1.6606</v>
+      </c>
+      <c r="G69" t="n">
         <v>1.7002</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>4.2609</v>
       </c>
     </row>
@@ -2448,9 +2657,12 @@
         <v>0.9772999999999999</v>
       </c>
       <c r="F70" t="n">
+        <v>1.6681</v>
+      </c>
+      <c r="G70" t="n">
         <v>1.7462</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>4.2849</v>
       </c>
     </row>
@@ -2477,9 +2689,12 @@
         <v>0.9814000000000001</v>
       </c>
       <c r="F71" t="n">
+        <v>1.6619</v>
+      </c>
+      <c r="G71" t="n">
         <v>1.6441</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>4.2651</v>
       </c>
     </row>
@@ -2506,9 +2721,12 @@
         <v>0.9744</v>
       </c>
       <c r="F72" t="n">
+        <v>1.6403</v>
+      </c>
+      <c r="G72" t="n">
         <v>1.7769</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>4.1949</v>
       </c>
     </row>
@@ -2535,9 +2753,12 @@
         <v>0.9696</v>
       </c>
       <c r="F73" t="n">
+        <v>1.3918</v>
+      </c>
+      <c r="G73" t="n">
         <v>1.6207</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>3.2815</v>
       </c>
     </row>
@@ -2564,9 +2785,12 @@
         <v>0.9776</v>
       </c>
       <c r="F74" t="n">
+        <v>1.4509</v>
+      </c>
+      <c r="G74" t="n">
         <v>1.4919</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>3.5201</v>
       </c>
     </row>
@@ -2593,9 +2817,12 @@
         <v>0.8868</v>
       </c>
       <c r="F75" t="n">
+        <v>1.9088</v>
+      </c>
+      <c r="G75" t="n">
         <v>2.8771</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>4.9976</v>
       </c>
     </row>
@@ -2622,9 +2849,12 @@
         <v>0.8868</v>
       </c>
       <c r="F76" t="n">
+        <v>1.9088</v>
+      </c>
+      <c r="G76" t="n">
         <v>2.8771</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>4.9976</v>
       </c>
     </row>
@@ -2651,9 +2881,12 @@
         <v>0.9717</v>
       </c>
       <c r="F77" t="n">
+        <v>1.6257</v>
+      </c>
+      <c r="G77" t="n">
         <v>1.5861</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>4.1467</v>
       </c>
     </row>
@@ -2680,9 +2913,12 @@
         <v>0.9733000000000001</v>
       </c>
       <c r="F78" t="n">
+        <v>1.6065</v>
+      </c>
+      <c r="G78" t="n">
         <v>1.5601</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>4.0827</v>
       </c>
     </row>
@@ -2709,9 +2945,12 @@
         <v>0.9738</v>
       </c>
       <c r="F79" t="n">
+        <v>1.6095</v>
+      </c>
+      <c r="G79" t="n">
         <v>1.5493</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>4.0928</v>
       </c>
     </row>
@@ -2738,9 +2977,12 @@
         <v>0.9733000000000001</v>
       </c>
       <c r="F80" t="n">
+        <v>1.607</v>
+      </c>
+      <c r="G80" t="n">
         <v>1.56</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>4.0844</v>
       </c>
     </row>
@@ -2767,9 +3009,12 @@
         <v>0.9795</v>
       </c>
       <c r="F81" t="n">
+        <v>1.1748</v>
+      </c>
+      <c r="G81" t="n">
         <v>1.1228</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>2.1917</v>
       </c>
     </row>
@@ -2796,9 +3041,12 @@
         <v>0.9779</v>
       </c>
       <c r="F82" t="n">
+        <v>1.1711</v>
+      </c>
+      <c r="G82" t="n">
         <v>1.1526</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>2.1685</v>
       </c>
     </row>
@@ -2825,9 +3073,12 @@
         <v>0.886</v>
       </c>
       <c r="F83" t="n">
+        <v>1.9114</v>
+      </c>
+      <c r="G83" t="n">
         <v>2.8865</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>5.0048</v>
       </c>
     </row>
@@ -2854,9 +3105,12 @@
         <v>0.8862</v>
       </c>
       <c r="F84" t="n">
+        <v>1.9053</v>
+      </c>
+      <c r="G84" t="n">
         <v>2.8828</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>4.988</v>
       </c>
     </row>
@@ -2883,9 +3137,12 @@
         <v>0.8869</v>
       </c>
       <c r="F85" t="n">
+        <v>1.9124</v>
+      </c>
+      <c r="G85" t="n">
         <v>2.8814</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>5.0076</v>
       </c>
     </row>
@@ -2912,9 +3169,12 @@
         <v>0.9744</v>
       </c>
       <c r="F86" t="n">
+        <v>1.7273</v>
+      </c>
+      <c r="G86" t="n">
         <v>1.7943</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>4.4708</v>
       </c>
     </row>
@@ -2941,9 +3201,12 @@
         <v>0.9797</v>
       </c>
       <c r="F87" t="n">
+        <v>1.6964</v>
+      </c>
+      <c r="G87" t="n">
         <v>1.7236</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>4.3746</v>
       </c>
     </row>
@@ -2970,9 +3233,12 @@
         <v>0.9636</v>
       </c>
       <c r="F88" t="n">
+        <v>1.6783</v>
+      </c>
+      <c r="G88" t="n">
         <v>2.0521</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>4.3175</v>
       </c>
     </row>
@@ -2999,9 +3265,12 @@
         <v>0.9734</v>
       </c>
       <c r="F89" t="n">
+        <v>1.6562</v>
+      </c>
+      <c r="G89" t="n">
         <v>1.778</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>4.2466</v>
       </c>
     </row>
@@ -3028,9 +3297,12 @@
         <v>0.9817</v>
       </c>
       <c r="F90" t="n">
+        <v>1.2415</v>
+      </c>
+      <c r="G90" t="n">
         <v>1.2412</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>2.576</v>
       </c>
     </row>
@@ -3057,9 +3329,12 @@
         <v>0.9876</v>
       </c>
       <c r="F91" t="n">
+        <v>1.2723</v>
+      </c>
+      <c r="G91" t="n">
         <v>1.0357</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>2.7356</v>
       </c>
     </row>
@@ -3086,9 +3361,12 @@
         <v>0.9636</v>
       </c>
       <c r="F92" t="n">
+        <v>1.6783</v>
+      </c>
+      <c r="G92" t="n">
         <v>2.0521</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>4.3175</v>
       </c>
     </row>
@@ -3115,9 +3393,12 @@
         <v>0.9876</v>
       </c>
       <c r="F93" t="n">
+        <v>1.2723</v>
+      </c>
+      <c r="G93" t="n">
         <v>1.0357</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>2.7356</v>
       </c>
     </row>
@@ -3144,9 +3425,12 @@
         <v>0.9333</v>
       </c>
       <c r="F94" t="n">
+        <v>1.7993</v>
+      </c>
+      <c r="G94" t="n">
         <v>2.2811</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>4.6869</v>
       </c>
     </row>
@@ -3173,9 +3457,12 @@
         <v>0.9615</v>
       </c>
       <c r="F95" t="n">
+        <v>1.9527</v>
+      </c>
+      <c r="G95" t="n">
         <v>2.0602</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>5.1169</v>
       </c>
     </row>
@@ -3202,9 +3489,12 @@
         <v>0.9338</v>
       </c>
       <c r="F96" t="n">
+        <v>1.804</v>
+      </c>
+      <c r="G96" t="n">
         <v>2.2709</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>4.7006</v>
       </c>
     </row>
@@ -3231,9 +3521,12 @@
         <v>0.9316</v>
       </c>
       <c r="F97" t="n">
+        <v>1.8017</v>
+      </c>
+      <c r="G97" t="n">
         <v>2.2918</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>4.694</v>
       </c>
     </row>
@@ -3260,9 +3553,12 @@
         <v>0.9689</v>
       </c>
       <c r="F98" t="n">
+        <v>1.4842</v>
+      </c>
+      <c r="G98" t="n">
         <v>1.5053</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>3.648</v>
       </c>
     </row>
@@ -3289,9 +3585,12 @@
         <v>0.9678</v>
       </c>
       <c r="F99" t="n">
+        <v>1.4972</v>
+      </c>
+      <c r="G99" t="n">
         <v>1.5328</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>3.6964</v>
       </c>
     </row>
@@ -3318,9 +3617,12 @@
         <v>0.975</v>
       </c>
       <c r="F100" t="n">
+        <v>1.5069</v>
+      </c>
+      <c r="G100" t="n">
         <v>1.4188</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>3.7323</v>
       </c>
     </row>
@@ -3347,9 +3649,12 @@
         <v>0.9639</v>
       </c>
       <c r="F101" t="n">
+        <v>1.5123</v>
+      </c>
+      <c r="G101" t="n">
         <v>1.6107</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>3.7523</v>
       </c>
     </row>
@@ -3376,9 +3681,12 @@
         <v>0.9729</v>
       </c>
       <c r="F102" t="n">
+        <v>1.522</v>
+      </c>
+      <c r="G102" t="n">
         <v>1.4578</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>3.7876</v>
       </c>
     </row>
@@ -3405,9 +3713,12 @@
         <v>0.9677</v>
       </c>
       <c r="F103" t="n">
+        <v>1.4858</v>
+      </c>
+      <c r="G103" t="n">
         <v>1.5807</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>3.654</v>
       </c>
     </row>
@@ -3434,9 +3745,12 @@
         <v>0.9472</v>
       </c>
       <c r="F104" t="n">
+        <v>1.4742</v>
+      </c>
+      <c r="G104" t="n">
         <v>1.8581</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>3.6099</v>
       </c>
     </row>
@@ -3463,9 +3777,12 @@
         <v>0.9442</v>
       </c>
       <c r="F105" t="n">
+        <v>1.4683</v>
+      </c>
+      <c r="G105" t="n">
         <v>1.8895</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>3.5873</v>
       </c>
     </row>
@@ -3492,9 +3809,12 @@
         <v>0.9764</v>
       </c>
       <c r="F106" t="n">
+        <v>1.4958</v>
+      </c>
+      <c r="G106" t="n">
         <v>1.368</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>3.6914</v>
       </c>
     </row>
@@ -3521,9 +3841,12 @@
         <v>0.9605</v>
       </c>
       <c r="F107" t="n">
+        <v>1.5062</v>
+      </c>
+      <c r="G107" t="n">
         <v>1.6608</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>3.7299</v>
       </c>
     </row>
@@ -3550,9 +3873,12 @@
         <v>0.9808</v>
       </c>
       <c r="F108" t="n">
+        <v>1.4491</v>
+      </c>
+      <c r="G108" t="n">
         <v>1.3578</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>3.5132</v>
       </c>
     </row>
@@ -3579,9 +3905,12 @@
         <v>0.9808</v>
       </c>
       <c r="F109" t="n">
+        <v>1.439</v>
+      </c>
+      <c r="G109" t="n">
         <v>1.303</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>3.4733</v>
       </c>
     </row>
@@ -3608,9 +3937,12 @@
         <v>0.9723000000000001</v>
       </c>
       <c r="F110" t="n">
+        <v>1.472</v>
+      </c>
+      <c r="G110" t="n">
         <v>1.4919</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>3.6017</v>
       </c>
     </row>
@@ -3637,9 +3969,12 @@
         <v>0.9748</v>
       </c>
       <c r="F111" t="n">
+        <v>1.4507</v>
+      </c>
+      <c r="G111" t="n">
         <v>1.4108</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>3.5195</v>
       </c>
     </row>
@@ -3666,9 +4001,12 @@
         <v>0.9852</v>
       </c>
       <c r="F112" t="n">
+        <v>1.3219</v>
+      </c>
+      <c r="G112" t="n">
         <v>1.1332</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>2.9745</v>
       </c>
     </row>
@@ -3695,9 +4033,12 @@
         <v>0.9752999999999999</v>
       </c>
       <c r="F113" t="n">
+        <v>1.3343</v>
+      </c>
+      <c r="G113" t="n">
         <v>1.4009</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>3.0312</v>
       </c>
     </row>
@@ -3724,9 +4065,12 @@
         <v>0.9749</v>
       </c>
       <c r="F114" t="n">
+        <v>1.4389</v>
+      </c>
+      <c r="G114" t="n">
         <v>1.4344</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>3.4732</v>
       </c>
     </row>
@@ -3753,9 +4097,12 @@
         <v>0.9751</v>
       </c>
       <c r="F115" t="n">
+        <v>1.4479</v>
+      </c>
+      <c r="G115" t="n">
         <v>1.41</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>3.5086</v>
       </c>
     </row>
@@ -3782,9 +4129,12 @@
         <v>0.9874000000000001</v>
       </c>
       <c r="F116" t="n">
+        <v>1.1895</v>
+      </c>
+      <c r="G116" t="n">
         <v>0.9113</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>2.2819</v>
       </c>
     </row>
@@ -3811,9 +4161,12 @@
         <v>0.9846</v>
       </c>
       <c r="F117" t="n">
+        <v>1.1915</v>
+      </c>
+      <c r="G117" t="n">
         <v>0.9919</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>2.2941</v>
       </c>
     </row>
@@ -3840,9 +4193,12 @@
         <v>0.9442</v>
       </c>
       <c r="F118" t="n">
+        <v>1.4683</v>
+      </c>
+      <c r="G118" t="n">
         <v>1.8895</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>3.5873</v>
       </c>
     </row>
@@ -3869,9 +4225,12 @@
         <v>0.9752999999999999</v>
       </c>
       <c r="F119" t="n">
+        <v>1.3343</v>
+      </c>
+      <c r="G119" t="n">
         <v>1.4009</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>3.0312</v>
       </c>
     </row>
@@ -3898,9 +4257,12 @@
         <v>0.9534</v>
       </c>
       <c r="F120" t="n">
+        <v>1.7672</v>
+      </c>
+      <c r="G120" t="n">
         <v>1.9436</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>4.5918</v>
       </c>
     </row>
@@ -3927,9 +4289,12 @@
         <v>0.9534</v>
       </c>
       <c r="F121" t="n">
+        <v>1.7672</v>
+      </c>
+      <c r="G121" t="n">
         <v>1.9436</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>4.5918</v>
       </c>
     </row>
@@ -3956,9 +4321,12 @@
         <v>0.9186</v>
       </c>
       <c r="F122" t="n">
+        <v>1.6359</v>
+      </c>
+      <c r="G122" t="n">
         <v>2.3893</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>4.1805</v>
       </c>
     </row>
@@ -3985,9 +4353,12 @@
         <v>0.9752</v>
       </c>
       <c r="F123" t="n">
+        <v>1.3351</v>
+      </c>
+      <c r="G123" t="n">
         <v>1.3999</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>3.0345</v>
       </c>
     </row>
@@ -4014,9 +4385,12 @@
         <v>0.9809</v>
       </c>
       <c r="F124" t="n">
+        <v>1.3878</v>
+      </c>
+      <c r="G124" t="n">
         <v>1.2889</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>3.2645</v>
       </c>
     </row>
@@ -4043,9 +4417,12 @@
         <v>0.9328</v>
       </c>
       <c r="F125" t="n">
+        <v>1.8014</v>
+      </c>
+      <c r="G125" t="n">
         <v>2.3012</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>4.693</v>
       </c>
     </row>
@@ -4072,9 +4449,12 @@
         <v>0.8752</v>
       </c>
       <c r="F126" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="G126" t="n">
         <v>2.9793</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>4.8756</v>
       </c>
     </row>
@@ -4101,9 +4481,12 @@
         <v>0.9752</v>
       </c>
       <c r="F127" t="n">
+        <v>1.3137</v>
+      </c>
+      <c r="G127" t="n">
         <v>1.2661</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>2.9362</v>
       </c>
     </row>
@@ -4130,9 +4513,12 @@
         <v>0.8732</v>
       </c>
       <c r="F128" t="n">
+        <v>1.8661</v>
+      </c>
+      <c r="G128" t="n">
         <v>2.9899</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>4.8788</v>
       </c>
     </row>
@@ -4159,9 +4545,12 @@
         <v>0.8737</v>
       </c>
       <c r="F129" t="n">
+        <v>1.8608</v>
+      </c>
+      <c r="G129" t="n">
         <v>2.9887</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>4.8638</v>
       </c>
     </row>
@@ -4188,9 +4577,12 @@
         <v>0.8741</v>
       </c>
       <c r="F130" t="n">
+        <v>1.8614</v>
+      </c>
+      <c r="G130" t="n">
         <v>2.9871</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>4.8654</v>
       </c>
     </row>
@@ -4217,9 +4609,12 @@
         <v>0.8744</v>
       </c>
       <c r="F131" t="n">
+        <v>1.8626</v>
+      </c>
+      <c r="G131" t="n">
         <v>2.9833</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>4.8688</v>
       </c>
     </row>
@@ -4246,9 +4641,12 @@
         <v>0.8749</v>
       </c>
       <c r="F132" t="n">
+        <v>1.8634</v>
+      </c>
+      <c r="G132" t="n">
         <v>2.9797</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>4.8711</v>
       </c>
     </row>
@@ -4275,9 +4673,12 @@
         <v>0.8751</v>
       </c>
       <c r="F133" t="n">
+        <v>1.8649</v>
+      </c>
+      <c r="G133" t="n">
         <v>2.9802</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>4.8753</v>
       </c>
     </row>
@@ -4304,9 +4705,12 @@
         <v>0.8754999999999999</v>
       </c>
       <c r="F134" t="n">
+        <v>1.8666</v>
+      </c>
+      <c r="G134" t="n">
         <v>2.9717</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>4.8802</v>
       </c>
     </row>
@@ -4333,9 +4737,12 @@
         <v>0.8736</v>
       </c>
       <c r="F135" t="n">
+        <v>1.8654</v>
+      </c>
+      <c r="G135" t="n">
         <v>2.9873</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>4.8769</v>
       </c>
     </row>
@@ -4362,9 +4769,12 @@
         <v>0.8744</v>
       </c>
       <c r="F136" t="n">
+        <v>1.8616</v>
+      </c>
+      <c r="G136" t="n">
         <v>2.9842</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>4.866</v>
       </c>
     </row>
@@ -4391,9 +4801,12 @@
         <v>0.9742</v>
       </c>
       <c r="F137" t="n">
+        <v>1.7445</v>
+      </c>
+      <c r="G137" t="n">
         <v>1.6944</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>4.5232</v>
       </c>
     </row>
@@ -4420,9 +4833,12 @@
         <v>0.9752</v>
       </c>
       <c r="F138" t="n">
+        <v>1.6958</v>
+      </c>
+      <c r="G138" t="n">
         <v>1.6785</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>4.3728</v>
       </c>
     </row>
@@ -4449,9 +4865,12 @@
         <v>0.9585</v>
       </c>
       <c r="F139" t="n">
+        <v>1.7539</v>
+      </c>
+      <c r="G139" t="n">
         <v>1.9407</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>4.5518</v>
       </c>
     </row>
@@ -4478,9 +4897,12 @@
         <v>0.976</v>
       </c>
       <c r="F140" t="n">
+        <v>1.3247</v>
+      </c>
+      <c r="G140" t="n">
         <v>1.4086</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>2.9874</v>
       </c>
     </row>
@@ -4507,9 +4929,12 @@
         <v>0.9872</v>
       </c>
       <c r="F141" t="n">
+        <v>1.3299</v>
+      </c>
+      <c r="G141" t="n">
         <v>1.1503</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>3.0109</v>
       </c>
     </row>
@@ -4536,9 +4961,12 @@
         <v>0.9752</v>
       </c>
       <c r="F142" t="n">
+        <v>1.6958</v>
+      </c>
+      <c r="G142" t="n">
         <v>1.6785</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>4.3728</v>
       </c>
     </row>
@@ -4565,9 +4993,12 @@
         <v>0.9627</v>
       </c>
       <c r="F143" t="n">
+        <v>1.7448</v>
+      </c>
+      <c r="G143" t="n">
         <v>1.8719</v>
       </c>
-      <c r="G143" t="n">
+      <c r="H143" t="n">
         <v>4.5242</v>
       </c>
     </row>
@@ -4594,9 +5025,12 @@
         <v>0.9636</v>
       </c>
       <c r="F144" t="n">
+        <v>1.7219</v>
+      </c>
+      <c r="G144" t="n">
         <v>1.8371</v>
       </c>
-      <c r="G144" t="n">
+      <c r="H144" t="n">
         <v>4.4542</v>
       </c>
     </row>
@@ -4623,9 +5057,12 @@
         <v>0.9872</v>
       </c>
       <c r="F145" t="n">
+        <v>1.3299</v>
+      </c>
+      <c r="G145" t="n">
         <v>1.1503</v>
       </c>
-      <c r="G145" t="n">
+      <c r="H145" t="n">
         <v>3.0109</v>
       </c>
     </row>
@@ -4652,9 +5089,12 @@
         <v>0.9631</v>
       </c>
       <c r="F146" t="n">
+        <v>1.3025</v>
+      </c>
+      <c r="G146" t="n">
         <v>1.5096</v>
       </c>
-      <c r="G146" t="n">
+      <c r="H146" t="n">
         <v>2.8832</v>
       </c>
     </row>
@@ -4681,9 +5121,12 @@
         <v>0.9633</v>
       </c>
       <c r="F147" t="n">
+        <v>1.3045</v>
+      </c>
+      <c r="G147" t="n">
         <v>1.5138</v>
       </c>
-      <c r="G147" t="n">
+      <c r="H147" t="n">
         <v>2.8926</v>
       </c>
     </row>
@@ -4710,9 +5153,12 @@
         <v>0.9762999999999999</v>
       </c>
       <c r="F148" t="n">
+        <v>1.3047</v>
+      </c>
+      <c r="G148" t="n">
         <v>1.2381</v>
       </c>
-      <c r="G148" t="n">
+      <c r="H148" t="n">
         <v>2.8936</v>
       </c>
     </row>
@@ -4739,9 +5185,12 @@
         <v>0.9843</v>
       </c>
       <c r="F149" t="n">
+        <v>1.3175</v>
+      </c>
+      <c r="G149" t="n">
         <v>1.0387</v>
       </c>
-      <c r="G149" t="n">
+      <c r="H149" t="n">
         <v>2.9537</v>
       </c>
     </row>
@@ -4768,9 +5217,12 @@
         <v>0.9626</v>
       </c>
       <c r="F150" t="n">
+        <v>1.3113</v>
+      </c>
+      <c r="G150" t="n">
         <v>1.5198</v>
       </c>
-      <c r="G150" t="n">
+      <c r="H150" t="n">
         <v>2.9247</v>
       </c>
     </row>
@@ -4797,9 +5249,12 @@
         <v>0.9631</v>
       </c>
       <c r="F151" t="n">
+        <v>1.3111</v>
+      </c>
+      <c r="G151" t="n">
         <v>1.509</v>
       </c>
-      <c r="G151" t="n">
+      <c r="H151" t="n">
         <v>2.924</v>
       </c>
     </row>
@@ -4826,9 +5281,12 @@
         <v>0.963</v>
       </c>
       <c r="F152" t="n">
+        <v>1.3108</v>
+      </c>
+      <c r="G152" t="n">
         <v>1.5154</v>
       </c>
-      <c r="G152" t="n">
+      <c r="H152" t="n">
         <v>2.9225</v>
       </c>
     </row>
@@ -4855,9 +5313,12 @@
         <v>0.963</v>
       </c>
       <c r="F153" t="n">
+        <v>1.3052</v>
+      </c>
+      <c r="G153" t="n">
         <v>1.5135</v>
       </c>
-      <c r="G153" t="n">
+      <c r="H153" t="n">
         <v>2.8959</v>
       </c>
     </row>
@@ -4884,9 +5345,12 @@
         <v>0.9641999999999999</v>
       </c>
       <c r="F154" t="n">
+        <v>1.3112</v>
+      </c>
+      <c r="G154" t="n">
         <v>1.4937</v>
       </c>
-      <c r="G154" t="n">
+      <c r="H154" t="n">
         <v>2.9245</v>
       </c>
     </row>
@@ -4913,9 +5377,12 @@
         <v>0.9771</v>
       </c>
       <c r="F155" t="n">
+        <v>1.196</v>
+      </c>
+      <c r="G155" t="n">
         <v>1.1705</v>
       </c>
-      <c r="G155" t="n">
+      <c r="H155" t="n">
         <v>2.3212</v>
       </c>
     </row>
@@ -4942,9 +5409,12 @@
         <v>0.9767</v>
       </c>
       <c r="F156" t="n">
+        <v>1.1885</v>
+      </c>
+      <c r="G156" t="n">
         <v>1.1714</v>
       </c>
-      <c r="G156" t="n">
+      <c r="H156" t="n">
         <v>2.276</v>
       </c>
     </row>
@@ -4971,9 +5441,12 @@
         <v>0.9755</v>
       </c>
       <c r="F157" t="n">
+        <v>1.1981</v>
+      </c>
+      <c r="G157" t="n">
         <v>1.2026</v>
       </c>
-      <c r="G157" t="n">
+      <c r="H157" t="n">
         <v>2.3332</v>
       </c>
     </row>
@@ -5000,9 +5473,12 @@
         <v>0.9898</v>
       </c>
       <c r="F158" t="n">
+        <v>1.1551</v>
+      </c>
+      <c r="G158" t="n">
         <v>0.8255</v>
       </c>
-      <c r="G158" t="n">
+      <c r="H158" t="n">
         <v>2.0644</v>
       </c>
     </row>
@@ -5029,9 +5505,12 @@
         <v>0.9073</v>
       </c>
       <c r="F159" t="n">
+        <v>1.8671</v>
+      </c>
+      <c r="G159" t="n">
         <v>2.6007</v>
       </c>
-      <c r="G159" t="n">
+      <c r="H159" t="n">
         <v>4.8816</v>
       </c>
     </row>
@@ -5058,9 +5537,12 @@
         <v>0.9520999999999999</v>
       </c>
       <c r="F160" t="n">
+        <v>1.3977</v>
+      </c>
+      <c r="G160" t="n">
         <v>1.7756</v>
       </c>
-      <c r="G160" t="n">
+      <c r="H160" t="n">
         <v>3.3058</v>
       </c>
     </row>
@@ -5087,9 +5569,12 @@
         <v>0.9516</v>
       </c>
       <c r="F161" t="n">
+        <v>1.3997</v>
+      </c>
+      <c r="G161" t="n">
         <v>1.7854</v>
       </c>
-      <c r="G161" t="n">
+      <c r="H161" t="n">
         <v>3.3142</v>
       </c>
     </row>
@@ -5116,9 +5601,12 @@
         <v>0.907</v>
       </c>
       <c r="F162" t="n">
+        <v>1.8679</v>
+      </c>
+      <c r="G162" t="n">
         <v>2.6082</v>
       </c>
-      <c r="G162" t="n">
+      <c r="H162" t="n">
         <v>4.8839</v>
       </c>
     </row>
@@ -5145,9 +5633,12 @@
         <v>0.9558</v>
       </c>
       <c r="F163" t="n">
+        <v>1.6782</v>
+      </c>
+      <c r="G163" t="n">
         <v>2.2022</v>
       </c>
-      <c r="G163" t="n">
+      <c r="H163" t="n">
         <v>4.3172</v>
       </c>
     </row>
@@ -5174,9 +5665,12 @@
         <v>0.9758</v>
       </c>
       <c r="F164" t="n">
+        <v>1.3253</v>
+      </c>
+      <c r="G164" t="n">
         <v>1.4116</v>
       </c>
-      <c r="G164" t="n">
+      <c r="H164" t="n">
         <v>2.9902</v>
       </c>
     </row>
@@ -5203,9 +5697,12 @@
         <v>0.9328</v>
       </c>
       <c r="F165" t="n">
+        <v>1.8014</v>
+      </c>
+      <c r="G165" t="n">
         <v>2.3012</v>
       </c>
-      <c r="G165" t="n">
+      <c r="H165" t="n">
         <v>4.693</v>
       </c>
     </row>
@@ -5232,9 +5729,12 @@
         <v>0.8195</v>
       </c>
       <c r="F166" t="n">
+        <v>1.9543</v>
+      </c>
+      <c r="G166" t="n">
         <v>3.425</v>
       </c>
-      <c r="G166" t="n">
+      <c r="H166" t="n">
         <v>5.1211</v>
       </c>
     </row>
@@ -5261,9 +5761,12 @@
         <v>0.9779</v>
       </c>
       <c r="F167" t="n">
+        <v>1.7305</v>
+      </c>
+      <c r="G167" t="n">
         <v>1.7255</v>
       </c>
-      <c r="G167" t="n">
+      <c r="H167" t="n">
         <v>4.4806</v>
       </c>
     </row>
@@ -5290,9 +5793,12 @@
         <v>0.9862</v>
       </c>
       <c r="F168" t="n">
+        <v>1.3011</v>
+      </c>
+      <c r="G168" t="n">
         <v>1.1082</v>
       </c>
-      <c r="G168" t="n">
+      <c r="H168" t="n">
         <v>2.8764</v>
       </c>
     </row>
@@ -5319,9 +5825,12 @@
         <v>0.9874000000000001</v>
       </c>
       <c r="F169" t="n">
+        <v>1.2044</v>
+      </c>
+      <c r="G169" t="n">
         <v>0.9214</v>
       </c>
-      <c r="G169" t="n">
+      <c r="H169" t="n">
         <v>2.37</v>
       </c>
     </row>
@@ -5348,9 +5857,12 @@
         <v>0.9758</v>
       </c>
       <c r="F170" t="n">
+        <v>1.4366</v>
+      </c>
+      <c r="G170" t="n">
         <v>1.6012</v>
       </c>
-      <c r="G170" t="n">
+      <c r="H170" t="n">
         <v>3.4639</v>
       </c>
     </row>
@@ -5377,9 +5889,12 @@
         <v>0.9816</v>
       </c>
       <c r="F171" t="n">
+        <v>1.2323</v>
+      </c>
+      <c r="G171" t="n">
         <v>1.2192</v>
       </c>
-      <c r="G171" t="n">
+      <c r="H171" t="n">
         <v>2.5267</v>
       </c>
     </row>
@@ -5406,9 +5921,12 @@
         <v>0.9725</v>
       </c>
       <c r="F172" t="n">
+        <v>1.6738</v>
+      </c>
+      <c r="G172" t="n">
         <v>1.7668</v>
       </c>
-      <c r="G172" t="n">
+      <c r="H172" t="n">
         <v>4.3031</v>
       </c>
     </row>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C16.0/RANDOMSEARCH_DETAILS_C16.0.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C16.0/RANDOMSEARCH_DETAILS_C16.0.xlsx
@@ -474,20 +474,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9821</v>
+        <v>0.9879</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1863</v>
+        <v>0.7923</v>
       </c>
       <c r="G2" t="n">
-        <v>1.0859</v>
+        <v>0.9115</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2626</v>
+        <v>2.3827</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9901</v>
+        <v>0.9825</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1904</v>
+        <v>0.7843</v>
       </c>
       <c r="G3" t="n">
-        <v>0.849</v>
+        <v>1.1036</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2874</v>
+        <v>2.4284</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9333</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7993</v>
+        <v>0.0873</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2811</v>
+        <v>2.9117</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6869</v>
+        <v>4.995</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9766</v>
+        <v>0.9591</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5493</v>
+        <v>0.4393</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4637</v>
+        <v>1.7985</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8853</v>
+        <v>3.915</v>
       </c>
     </row>
     <row r="6">
@@ -602,20 +602,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.9758</v>
+        <v>0.9529</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6053</v>
+        <v>0.4124</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4916</v>
+        <v>1.8949</v>
       </c>
       <c r="H6" t="n">
-        <v>4.0786</v>
+        <v>4.0081</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.886</v>
+        <v>0.879</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8851</v>
+        <v>0.1869</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9126</v>
+        <v>2.9514</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9319</v>
+        <v>4.7148</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8838</v>
+        <v>0.9081</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9255</v>
+        <v>0.127</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9491</v>
+        <v>2.6466</v>
       </c>
       <c r="H8" t="n">
-        <v>5.0434</v>
+        <v>4.8851</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9861</v>
+        <v>0.9852</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2207</v>
+        <v>0.7237</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0419</v>
+        <v>1.0428</v>
       </c>
       <c r="H9" t="n">
-        <v>2.463</v>
+        <v>2.7482</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.8512</v>
+        <v>0.925</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9313</v>
+        <v>0.142</v>
       </c>
       <c r="G10" t="n">
-        <v>3.2181</v>
+        <v>2.4683</v>
       </c>
       <c r="H10" t="n">
-        <v>5.0591</v>
+        <v>4.8431</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8821</v>
+        <v>0.9025</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9227</v>
+        <v>0.1375</v>
       </c>
       <c r="G11" t="n">
-        <v>2.9452</v>
+        <v>2.6792</v>
       </c>
       <c r="H11" t="n">
-        <v>5.0357</v>
+        <v>4.8556</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.8815</v>
+        <v>0.8991</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9293</v>
+        <v>0.1262</v>
       </c>
       <c r="G12" t="n">
-        <v>2.9526</v>
+        <v>2.7057</v>
       </c>
       <c r="H12" t="n">
-        <v>5.0537</v>
+        <v>4.8874</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9665</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9312</v>
+        <v>0.1239</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8927</v>
+        <v>1.8874</v>
       </c>
       <c r="H13" t="n">
-        <v>5.0588</v>
+        <v>4.8938</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.8799</v>
+        <v>0.9021</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9239</v>
+        <v>0.1398</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9605</v>
+        <v>2.6906</v>
       </c>
       <c r="H14" t="n">
-        <v>5.0389</v>
+        <v>4.8492</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.8818</v>
+        <v>0.9006</v>
       </c>
       <c r="F15" t="n">
-        <v>1.923</v>
+        <v>0.139</v>
       </c>
       <c r="G15" t="n">
-        <v>2.9693</v>
+        <v>2.6912</v>
       </c>
       <c r="H15" t="n">
-        <v>5.0364</v>
+        <v>4.8515</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8815</v>
+        <v>0.9001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.93</v>
+        <v>0.1328</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9568</v>
+        <v>2.6996</v>
       </c>
       <c r="H16" t="n">
-        <v>5.0555</v>
+        <v>4.8689</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.8811</v>
+        <v>0.9488</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9302</v>
+        <v>0.1238</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9617</v>
+        <v>2.1761</v>
       </c>
       <c r="H17" t="n">
-        <v>5.0561</v>
+        <v>4.8941</v>
       </c>
     </row>
     <row r="18">
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9805</v>
+        <v>0.9784</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7299</v>
+        <v>0.3128</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5942</v>
+        <v>1.625</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4788</v>
+        <v>4.3344</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9762</v>
+        <v>0.9816</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7562</v>
+        <v>0.2596</v>
       </c>
       <c r="G19" t="n">
-        <v>1.699</v>
+        <v>1.6314</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5588</v>
+        <v>4.4989</v>
       </c>
     </row>
     <row r="20">
@@ -1054,16 +1054,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9806</v>
+        <v>0.9801</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7632</v>
+        <v>0.2604</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6459</v>
+        <v>1.6518</v>
       </c>
       <c r="H20" t="n">
-        <v>4.5799</v>
+        <v>4.4965</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9734</v>
+        <v>0.9792</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7702</v>
+        <v>0.2601</v>
       </c>
       <c r="G21" t="n">
-        <v>1.7493</v>
+        <v>1.6651</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6007</v>
+        <v>4.4973</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9555</v>
+        <v>0.9748</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7609</v>
+        <v>0.2729</v>
       </c>
       <c r="G22" t="n">
-        <v>2.0783</v>
+        <v>1.7321</v>
       </c>
       <c r="H22" t="n">
-        <v>4.5729</v>
+        <v>4.4582</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9685</v>
+        <v>0.9654</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7484</v>
+        <v>0.2716</v>
       </c>
       <c r="G23" t="n">
-        <v>1.8485</v>
+        <v>1.8806</v>
       </c>
       <c r="H23" t="n">
-        <v>4.535</v>
+        <v>4.4625</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9647</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7561</v>
+        <v>0.2498</v>
       </c>
       <c r="G24" t="n">
-        <v>1.9213</v>
+        <v>1.9091</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5584</v>
+        <v>4.5286</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9721</v>
+        <v>0.9123</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7767</v>
+        <v>0.2432</v>
       </c>
       <c r="G25" t="n">
-        <v>1.6756</v>
+        <v>2.6179</v>
       </c>
       <c r="H25" t="n">
-        <v>4.6202</v>
+        <v>4.5484</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9557</v>
+        <v>0.9556</v>
       </c>
       <c r="F26" t="n">
-        <v>1.78</v>
+        <v>0.2533</v>
       </c>
       <c r="G26" t="n">
-        <v>2.2106</v>
+        <v>2.2004</v>
       </c>
       <c r="H26" t="n">
-        <v>4.6298</v>
+        <v>4.518</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9745</v>
+        <v>0.9565</v>
       </c>
       <c r="F27" t="n">
-        <v>1.7056</v>
+        <v>0.3028</v>
       </c>
       <c r="G27" t="n">
-        <v>1.7914</v>
+        <v>2.1285</v>
       </c>
       <c r="H27" t="n">
-        <v>4.4037</v>
+        <v>4.3658</v>
       </c>
     </row>
     <row r="28">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.974</v>
+        <v>0.9777</v>
       </c>
       <c r="F28" t="n">
-        <v>1.7245</v>
+        <v>0.2813</v>
       </c>
       <c r="G28" t="n">
-        <v>1.8451</v>
+        <v>1.7293</v>
       </c>
       <c r="H28" t="n">
-        <v>4.4621</v>
+        <v>4.4326</v>
       </c>
     </row>
     <row r="29">
@@ -1338,20 +1338,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9691</v>
+        <v>0.9746</v>
       </c>
       <c r="F29" t="n">
-        <v>1.7431</v>
+        <v>0.2666</v>
       </c>
       <c r="G29" t="n">
-        <v>1.8571</v>
+        <v>1.7835</v>
       </c>
       <c r="H29" t="n">
-        <v>4.519</v>
+        <v>4.4776</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9722</v>
+        <v>0.9792</v>
       </c>
       <c r="F30" t="n">
-        <v>1.7638</v>
+        <v>0.2628</v>
       </c>
       <c r="G30" t="n">
-        <v>1.7236</v>
+        <v>1.649</v>
       </c>
       <c r="H30" t="n">
-        <v>4.5816</v>
+        <v>4.4891</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9665</v>
       </c>
       <c r="F31" t="n">
-        <v>1.7587</v>
+        <v>0.2717</v>
       </c>
       <c r="G31" t="n">
-        <v>1.8843</v>
+        <v>1.959</v>
       </c>
       <c r="H31" t="n">
-        <v>4.5662</v>
+        <v>4.4619</v>
       </c>
     </row>
     <row r="32">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9735</v>
+        <v>0.9772</v>
       </c>
       <c r="F32" t="n">
-        <v>1.7205</v>
+        <v>0.294</v>
       </c>
       <c r="G32" t="n">
-        <v>1.7825</v>
+        <v>1.675</v>
       </c>
       <c r="H32" t="n">
-        <v>4.4497</v>
+        <v>4.3931</v>
       </c>
     </row>
     <row r="33">
@@ -1470,16 +1470,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9764</v>
+        <v>0.9729</v>
       </c>
       <c r="F33" t="n">
-        <v>1.6616</v>
+        <v>0.3011</v>
       </c>
       <c r="G33" t="n">
-        <v>1.6368</v>
+        <v>1.7103</v>
       </c>
       <c r="H33" t="n">
-        <v>4.2642</v>
+        <v>4.3712</v>
       </c>
     </row>
     <row r="34">
@@ -1498,20 +1498,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9876</v>
+        <v>0.977</v>
       </c>
       <c r="F34" t="n">
-        <v>1.2493</v>
+        <v>0.6803</v>
       </c>
       <c r="G34" t="n">
-        <v>1.0768</v>
+        <v>1.3684</v>
       </c>
       <c r="H34" t="n">
-        <v>2.6177</v>
+        <v>2.9563</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9855</v>
+        <v>0.989</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2441</v>
+        <v>0.6782</v>
       </c>
       <c r="G35" t="n">
-        <v>1.1214</v>
+        <v>1.0514</v>
       </c>
       <c r="H35" t="n">
-        <v>2.5903</v>
+        <v>2.9659</v>
       </c>
     </row>
     <row r="36">
@@ -1566,16 +1566,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9761</v>
       </c>
       <c r="F36" t="n">
-        <v>1.2718</v>
+        <v>0.6633</v>
       </c>
       <c r="G36" t="n">
-        <v>1.3379</v>
+        <v>1.3699</v>
       </c>
       <c r="H36" t="n">
-        <v>2.7331</v>
+        <v>3.0337</v>
       </c>
     </row>
     <row r="37">
@@ -1594,20 +1594,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9867</v>
+        <v>0.977</v>
       </c>
       <c r="F37" t="n">
-        <v>1.2961</v>
+        <v>0.6771</v>
       </c>
       <c r="G37" t="n">
-        <v>1.0996</v>
+        <v>1.3731</v>
       </c>
       <c r="H37" t="n">
-        <v>2.8525</v>
+        <v>2.9712</v>
       </c>
     </row>
     <row r="38">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9877</v>
+        <v>0.9847</v>
       </c>
       <c r="F38" t="n">
-        <v>1.284</v>
+        <v>0.6659</v>
       </c>
       <c r="G38" t="n">
-        <v>1.0577</v>
+        <v>1.1538</v>
       </c>
       <c r="H38" t="n">
-        <v>2.794</v>
+        <v>3.0222</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9733000000000001</v>
+        <v>0.975</v>
       </c>
       <c r="F39" t="n">
-        <v>1.2766</v>
+        <v>0.6895</v>
       </c>
       <c r="G39" t="n">
-        <v>1.4178</v>
+        <v>1.3671</v>
       </c>
       <c r="H39" t="n">
-        <v>2.7572</v>
+        <v>2.9134</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9785</v>
+        <v>0.9597</v>
       </c>
       <c r="F40" t="n">
-        <v>1.3304</v>
+        <v>0.6334</v>
       </c>
       <c r="G40" t="n">
-        <v>1.2619</v>
+        <v>1.6159</v>
       </c>
       <c r="H40" t="n">
-        <v>3.0132</v>
+        <v>3.1657</v>
       </c>
     </row>
     <row r="41">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9887</v>
+        <v>0.9799</v>
       </c>
       <c r="F41" t="n">
-        <v>1.2428</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>1.0584</v>
+        <v>1.3036</v>
       </c>
       <c r="H41" t="n">
-        <v>2.5834</v>
+        <v>2.9065</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9863</v>
+        <v>0.98</v>
       </c>
       <c r="F42" t="n">
-        <v>1.2486</v>
+        <v>0.7166</v>
       </c>
       <c r="G42" t="n">
-        <v>1.1141</v>
+        <v>1.3063</v>
       </c>
       <c r="H42" t="n">
-        <v>2.6137</v>
+        <v>2.7836</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9817</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>1.2413</v>
+        <v>0.7143</v>
       </c>
       <c r="G43" t="n">
-        <v>1.2416</v>
+        <v>1.0479</v>
       </c>
       <c r="H43" t="n">
-        <v>2.5749</v>
+        <v>2.7947</v>
       </c>
     </row>
     <row r="44">
@@ -1818,20 +1818,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9876</v>
+        <v>0.9895</v>
       </c>
       <c r="F44" t="n">
-        <v>1.2722</v>
+        <v>0.7033</v>
       </c>
       <c r="G44" t="n">
-        <v>1.0362</v>
+        <v>1.0005</v>
       </c>
       <c r="H44" t="n">
-        <v>2.7353</v>
+        <v>2.8482</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9877</v>
+        <v>0.9741</v>
       </c>
       <c r="F45" t="n">
-        <v>1.2865</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>1.0535</v>
+        <v>1.431</v>
       </c>
       <c r="H45" t="n">
-        <v>2.8059</v>
+        <v>3.0271</v>
       </c>
     </row>
     <row r="46">
@@ -1882,20 +1882,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9736</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>1.2851</v>
+        <v>0.696</v>
       </c>
       <c r="G46" t="n">
-        <v>1.4351</v>
+        <v>1.3978</v>
       </c>
       <c r="H46" t="n">
-        <v>2.7991</v>
+        <v>2.8827</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9705</v>
+        <v>0.9673</v>
       </c>
       <c r="F47" t="n">
-        <v>1.3065</v>
+        <v>0.6553</v>
       </c>
       <c r="G47" t="n">
-        <v>1.4937</v>
+        <v>1.5604</v>
       </c>
       <c r="H47" t="n">
-        <v>2.9024</v>
+        <v>3.0698</v>
       </c>
     </row>
     <row r="48">
@@ -1950,16 +1950,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9699</v>
       </c>
       <c r="F48" t="n">
-        <v>1.615</v>
+        <v>0.3204</v>
       </c>
       <c r="G48" t="n">
-        <v>1.8749</v>
+        <v>1.9887</v>
       </c>
       <c r="H48" t="n">
-        <v>4.1113</v>
+        <v>4.3101</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9801</v>
+        <v>0.9887</v>
       </c>
       <c r="F49" t="n">
-        <v>1.246</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>1.2784</v>
+        <v>1.0538</v>
       </c>
       <c r="H49" t="n">
-        <v>2.5999</v>
+        <v>2.7903</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9825</v>
+        <v>0.9882</v>
       </c>
       <c r="F50" t="n">
-        <v>1.1786</v>
+        <v>0.8197</v>
       </c>
       <c r="G50" t="n">
-        <v>1.0921</v>
+        <v>0.9257</v>
       </c>
       <c r="H50" t="n">
-        <v>2.2154</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9851</v>
       </c>
       <c r="F51" t="n">
-        <v>1.2313</v>
+        <v>0.7524</v>
       </c>
       <c r="G51" t="n">
-        <v>1.368</v>
+        <v>1.006</v>
       </c>
       <c r="H51" t="n">
-        <v>2.5214</v>
+        <v>2.6017</v>
       </c>
     </row>
     <row r="52">
@@ -2074,20 +2074,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.9835</v>
+        <v>0.9812</v>
       </c>
       <c r="F52" t="n">
-        <v>1.2285</v>
+        <v>0.7561</v>
       </c>
       <c r="G52" t="n">
-        <v>1.0278</v>
+        <v>1.0867</v>
       </c>
       <c r="H52" t="n">
-        <v>2.506</v>
+        <v>2.5819</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9838</v>
+        <v>0.988</v>
       </c>
       <c r="F53" t="n">
-        <v>1.1954</v>
+        <v>0.7904</v>
       </c>
       <c r="G53" t="n">
-        <v>1.0386</v>
+        <v>0.8789</v>
       </c>
       <c r="H53" t="n">
-        <v>2.3175</v>
+        <v>2.3937</v>
       </c>
     </row>
     <row r="54">
@@ -2142,16 +2142,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.9819</v>
+        <v>0.9809</v>
       </c>
       <c r="F54" t="n">
-        <v>1.1967</v>
+        <v>0.7904</v>
       </c>
       <c r="G54" t="n">
-        <v>1.0448</v>
+        <v>1.0909</v>
       </c>
       <c r="H54" t="n">
-        <v>2.3252</v>
+        <v>2.3939</v>
       </c>
     </row>
     <row r="55">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9887</v>
+        <v>0.9859</v>
       </c>
       <c r="F55" t="n">
-        <v>1.1799</v>
+        <v>0.7992</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8409</v>
+        <v>0.9428</v>
       </c>
       <c r="H55" t="n">
-        <v>2.2236</v>
+        <v>2.3431</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9831</v>
+        <v>0.9891</v>
       </c>
       <c r="F56" t="n">
-        <v>1.1792</v>
+        <v>0.799</v>
       </c>
       <c r="G56" t="n">
-        <v>1.0755</v>
+        <v>0.8904</v>
       </c>
       <c r="H56" t="n">
-        <v>2.2193</v>
+        <v>2.344</v>
       </c>
     </row>
     <row r="57">
@@ -2238,16 +2238,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9879</v>
+        <v>0.9877</v>
       </c>
       <c r="F57" t="n">
-        <v>1.1863</v>
+        <v>0.7952</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.9544</v>
       </c>
       <c r="H57" t="n">
-        <v>2.2627</v>
+        <v>2.366</v>
       </c>
     </row>
     <row r="58">
@@ -2266,20 +2266,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.9757</v>
+        <v>0.9522</v>
       </c>
       <c r="F58" t="n">
-        <v>1.5946</v>
+        <v>0.4132</v>
       </c>
       <c r="G58" t="n">
-        <v>1.4835</v>
+        <v>1.8993</v>
       </c>
       <c r="H58" t="n">
-        <v>4.0425</v>
+        <v>4.0051</v>
       </c>
     </row>
     <row r="59">
@@ -2298,20 +2298,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.9757</v>
+        <v>0.9528</v>
       </c>
       <c r="F59" t="n">
-        <v>1.5818</v>
+        <v>0.413</v>
       </c>
       <c r="G59" t="n">
-        <v>1.4929</v>
+        <v>1.8907</v>
       </c>
       <c r="H59" t="n">
-        <v>3.9987</v>
+        <v>4.006</v>
       </c>
     </row>
     <row r="60">
@@ -2330,20 +2330,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.9768</v>
+        <v>0.9534</v>
       </c>
       <c r="F60" t="n">
-        <v>1.5876</v>
+        <v>0.4126</v>
       </c>
       <c r="G60" t="n">
-        <v>1.4807</v>
+        <v>1.8838</v>
       </c>
       <c r="H60" t="n">
-        <v>4.0184</v>
+        <v>4.0073</v>
       </c>
     </row>
     <row r="61">
@@ -2362,20 +2362,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.9759</v>
+        <v>0.9533</v>
       </c>
       <c r="F61" t="n">
-        <v>1.5887</v>
+        <v>0.4117</v>
       </c>
       <c r="G61" t="n">
-        <v>1.4734</v>
+        <v>1.8888</v>
       </c>
       <c r="H61" t="n">
-        <v>4.0224</v>
+        <v>4.0104</v>
       </c>
     </row>
     <row r="62">
@@ -2394,20 +2394,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.9777</v>
+        <v>0.9853</v>
       </c>
       <c r="F62" t="n">
-        <v>1.1788</v>
+        <v>0.8014</v>
       </c>
       <c r="G62" t="n">
-        <v>1.1579</v>
+        <v>0.9579</v>
       </c>
       <c r="H62" t="n">
-        <v>2.2168</v>
+        <v>2.3299</v>
       </c>
     </row>
     <row r="63">
@@ -2426,20 +2426,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.9786</v>
+        <v>0.986</v>
       </c>
       <c r="F63" t="n">
-        <v>1.1753</v>
+        <v>0.8099</v>
       </c>
       <c r="G63" t="n">
-        <v>1.1329</v>
+        <v>0.9379</v>
       </c>
       <c r="H63" t="n">
-        <v>2.1952</v>
+        <v>2.2797</v>
       </c>
     </row>
     <row r="64">
@@ -2458,20 +2458,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.9782</v>
+        <v>0.9761</v>
       </c>
       <c r="F64" t="n">
-        <v>1.1664</v>
+        <v>0.8133</v>
       </c>
       <c r="G64" t="n">
-        <v>1.141</v>
+        <v>1.19</v>
       </c>
       <c r="H64" t="n">
-        <v>2.1384</v>
+        <v>2.2589</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.9787</v>
+        <v>0.9768</v>
       </c>
       <c r="F65" t="n">
-        <v>1.171</v>
+        <v>0.8114</v>
       </c>
       <c r="G65" t="n">
-        <v>1.1321</v>
+        <v>1.1783</v>
       </c>
       <c r="H65" t="n">
-        <v>2.1678</v>
+        <v>2.2705</v>
       </c>
     </row>
     <row r="66">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9891</v>
+        <v>0.9888</v>
       </c>
       <c r="F66" t="n">
-        <v>1.1893</v>
+        <v>0.8006</v>
       </c>
       <c r="G66" t="n">
-        <v>0.908</v>
+        <v>0.9195</v>
       </c>
       <c r="H66" t="n">
-        <v>2.2811</v>
+        <v>2.335</v>
       </c>
     </row>
     <row r="67">
@@ -2558,16 +2558,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9819</v>
+        <v>0.9816</v>
       </c>
       <c r="F67" t="n">
-        <v>1.1682</v>
+        <v>0.8158</v>
       </c>
       <c r="G67" t="n">
-        <v>1.0771</v>
+        <v>1.1128</v>
       </c>
       <c r="H67" t="n">
-        <v>2.1503</v>
+        <v>2.2443</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.988</v>
+        <v>0.9892</v>
       </c>
       <c r="F68" t="n">
-        <v>1.1836</v>
+        <v>0.7978</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9233</v>
+        <v>0.9152</v>
       </c>
       <c r="H68" t="n">
-        <v>2.246</v>
+        <v>2.3512</v>
       </c>
     </row>
     <row r="69">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9796</v>
+        <v>0.9799</v>
       </c>
       <c r="F69" t="n">
-        <v>1.6606</v>
+        <v>0.3077</v>
       </c>
       <c r="G69" t="n">
-        <v>1.7002</v>
+        <v>1.6228</v>
       </c>
       <c r="H69" t="n">
-        <v>4.2609</v>
+        <v>4.3503</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9577</v>
       </c>
       <c r="F70" t="n">
-        <v>1.6681</v>
+        <v>0.3035</v>
       </c>
       <c r="G70" t="n">
-        <v>1.7462</v>
+        <v>2.1399</v>
       </c>
       <c r="H70" t="n">
-        <v>4.2849</v>
+        <v>4.3636</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9646</v>
       </c>
       <c r="F71" t="n">
-        <v>1.6619</v>
+        <v>0.328</v>
       </c>
       <c r="G71" t="n">
-        <v>1.6441</v>
+        <v>2.06</v>
       </c>
       <c r="H71" t="n">
-        <v>4.2651</v>
+        <v>4.2861</v>
       </c>
     </row>
     <row r="72">
@@ -2718,16 +2718,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9744</v>
+        <v>0.9756</v>
       </c>
       <c r="F72" t="n">
-        <v>1.6403</v>
+        <v>0.326</v>
       </c>
       <c r="G72" t="n">
-        <v>1.7769</v>
+        <v>1.7671</v>
       </c>
       <c r="H72" t="n">
-        <v>4.1949</v>
+        <v>4.2925</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9696</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F73" t="n">
-        <v>1.3918</v>
+        <v>0.553</v>
       </c>
       <c r="G73" t="n">
-        <v>1.6207</v>
+        <v>1.6079</v>
       </c>
       <c r="H73" t="n">
-        <v>3.2815</v>
+        <v>3.4956</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9776</v>
+        <v>0.9807</v>
       </c>
       <c r="F74" t="n">
-        <v>1.4509</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>1.4919</v>
+        <v>1.416</v>
       </c>
       <c r="H74" t="n">
-        <v>3.5201</v>
+        <v>3.5776</v>
       </c>
     </row>
     <row r="75">
@@ -2814,16 +2814,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.8868</v>
+        <v>0.8945</v>
       </c>
       <c r="F75" t="n">
-        <v>1.9088</v>
+        <v>0.1482</v>
       </c>
       <c r="G75" t="n">
-        <v>2.8771</v>
+        <v>2.8337</v>
       </c>
       <c r="H75" t="n">
-        <v>4.9976</v>
+        <v>4.8254</v>
       </c>
     </row>
     <row r="76">
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.8868</v>
+        <v>0.8945</v>
       </c>
       <c r="F76" t="n">
-        <v>1.9088</v>
+        <v>0.1482</v>
       </c>
       <c r="G76" t="n">
-        <v>2.8771</v>
+        <v>2.8337</v>
       </c>
       <c r="H76" t="n">
-        <v>4.9976</v>
+        <v>4.8254</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.9717</v>
+        <v>0.9628</v>
       </c>
       <c r="F77" t="n">
-        <v>1.6257</v>
+        <v>0.3877</v>
       </c>
       <c r="G77" t="n">
-        <v>1.5861</v>
+        <v>1.7189</v>
       </c>
       <c r="H77" t="n">
-        <v>4.1467</v>
+        <v>4.0912</v>
       </c>
     </row>
     <row r="78">
@@ -2906,17 +2906,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.9733000000000001</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="F78" t="n">
-        <v>1.6065</v>
+        <v>0.3903</v>
       </c>
       <c r="G78" t="n">
-        <v>1.5601</v>
+        <v>1.9103</v>
       </c>
       <c r="H78" t="n">
         <v>4.0827</v>
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.9738</v>
+        <v>0.961</v>
       </c>
       <c r="F79" t="n">
-        <v>1.6095</v>
+        <v>0.3899</v>
       </c>
       <c r="G79" t="n">
-        <v>1.5493</v>
+        <v>1.749</v>
       </c>
       <c r="H79" t="n">
-        <v>4.0928</v>
+        <v>4.0839</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.9733000000000001</v>
+        <v>0.951</v>
       </c>
       <c r="F80" t="n">
-        <v>1.607</v>
+        <v>0.39</v>
       </c>
       <c r="G80" t="n">
-        <v>1.56</v>
+        <v>1.9114</v>
       </c>
       <c r="H80" t="n">
-        <v>4.0844</v>
+        <v>4.0835</v>
       </c>
     </row>
     <row r="81">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.9795</v>
+        <v>0.978</v>
       </c>
       <c r="F81" t="n">
-        <v>1.1748</v>
+        <v>0.8118</v>
       </c>
       <c r="G81" t="n">
-        <v>1.1228</v>
+        <v>1.162</v>
       </c>
       <c r="H81" t="n">
-        <v>2.1917</v>
+        <v>2.2685</v>
       </c>
     </row>
     <row r="82">
@@ -3034,20 +3034,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.9779</v>
+        <v>0.9764</v>
       </c>
       <c r="F82" t="n">
-        <v>1.1711</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>1.1526</v>
+        <v>1.1897</v>
       </c>
       <c r="H82" t="n">
-        <v>2.1685</v>
+        <v>2.2486</v>
       </c>
     </row>
     <row r="83">
@@ -3070,16 +3070,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.886</v>
+        <v>0.8868</v>
       </c>
       <c r="F83" t="n">
-        <v>1.9114</v>
+        <v>0.1519</v>
       </c>
       <c r="G83" t="n">
-        <v>2.8865</v>
+        <v>2.8788</v>
       </c>
       <c r="H83" t="n">
-        <v>5.0048</v>
+        <v>4.815</v>
       </c>
     </row>
     <row r="84">
@@ -3102,16 +3102,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.8862</v>
+        <v>0.8867</v>
       </c>
       <c r="F84" t="n">
-        <v>1.9053</v>
+        <v>0.1492</v>
       </c>
       <c r="G84" t="n">
-        <v>2.8828</v>
+        <v>2.8733</v>
       </c>
       <c r="H84" t="n">
-        <v>4.988</v>
+        <v>4.8227</v>
       </c>
     </row>
     <row r="85">
@@ -3134,16 +3134,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.8869</v>
+        <v>0.8865</v>
       </c>
       <c r="F85" t="n">
-        <v>1.9124</v>
+        <v>0.1491</v>
       </c>
       <c r="G85" t="n">
-        <v>2.8814</v>
+        <v>2.884</v>
       </c>
       <c r="H85" t="n">
-        <v>5.0076</v>
+        <v>4.8231</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9744</v>
+        <v>0.9802</v>
       </c>
       <c r="F86" t="n">
-        <v>1.7273</v>
+        <v>0.2863</v>
       </c>
       <c r="G86" t="n">
-        <v>1.7943</v>
+        <v>1.7121</v>
       </c>
       <c r="H86" t="n">
-        <v>4.4708</v>
+        <v>4.4171</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9797</v>
+        <v>0.9633</v>
       </c>
       <c r="F87" t="n">
-        <v>1.6964</v>
+        <v>0.2844</v>
       </c>
       <c r="G87" t="n">
-        <v>1.7236</v>
+        <v>2.1043</v>
       </c>
       <c r="H87" t="n">
-        <v>4.3746</v>
+        <v>4.4231</v>
       </c>
     </row>
     <row r="88">
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9636</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="F88" t="n">
-        <v>1.6783</v>
+        <v>0.3077</v>
       </c>
       <c r="G88" t="n">
-        <v>2.0521</v>
+        <v>2.1147</v>
       </c>
       <c r="H88" t="n">
-        <v>4.3175</v>
+        <v>4.3502</v>
       </c>
     </row>
     <row r="89">
@@ -3262,16 +3262,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9734</v>
+        <v>0.9755</v>
       </c>
       <c r="F89" t="n">
-        <v>1.6562</v>
+        <v>0.3061</v>
       </c>
       <c r="G89" t="n">
-        <v>1.778</v>
+        <v>1.7943</v>
       </c>
       <c r="H89" t="n">
-        <v>4.2466</v>
+        <v>4.3554</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9817</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="F90" t="n">
-        <v>1.2415</v>
+        <v>0.714</v>
       </c>
       <c r="G90" t="n">
-        <v>1.2412</v>
+        <v>1.0473</v>
       </c>
       <c r="H90" t="n">
-        <v>2.576</v>
+        <v>2.7961</v>
       </c>
     </row>
     <row r="91">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9876</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="F91" t="n">
-        <v>1.2723</v>
+        <v>0.7026</v>
       </c>
       <c r="G91" t="n">
-        <v>1.0357</v>
+        <v>1.0058</v>
       </c>
       <c r="H91" t="n">
-        <v>2.7356</v>
+        <v>2.8511</v>
       </c>
     </row>
     <row r="92">
@@ -3358,16 +3358,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9636</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="F92" t="n">
-        <v>1.6783</v>
+        <v>0.3077</v>
       </c>
       <c r="G92" t="n">
-        <v>2.0521</v>
+        <v>2.1147</v>
       </c>
       <c r="H92" t="n">
-        <v>4.3175</v>
+        <v>4.3502</v>
       </c>
     </row>
     <row r="93">
@@ -3386,20 +3386,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9876</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>1.2723</v>
+        <v>0.7026</v>
       </c>
       <c r="G93" t="n">
-        <v>1.0357</v>
+        <v>1.0058</v>
       </c>
       <c r="H93" t="n">
-        <v>2.7356</v>
+        <v>2.8511</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9333</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="F94" t="n">
-        <v>1.7993</v>
+        <v>0.0873</v>
       </c>
       <c r="G94" t="n">
-        <v>2.2811</v>
+        <v>2.9117</v>
       </c>
       <c r="H94" t="n">
-        <v>4.6869</v>
+        <v>4.995</v>
       </c>
     </row>
     <row r="95">
@@ -3450,20 +3450,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.9615</v>
+        <v>0.8215</v>
       </c>
       <c r="F95" t="n">
-        <v>1.9527</v>
+        <v>0.0075</v>
       </c>
       <c r="G95" t="n">
-        <v>2.0602</v>
+        <v>3.4964</v>
       </c>
       <c r="H95" t="n">
-        <v>5.1169</v>
+        <v>5.2088</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9338</v>
+        <v>0.9405</v>
       </c>
       <c r="F96" t="n">
-        <v>1.804</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="G96" t="n">
-        <v>2.2709</v>
+        <v>2.1988</v>
       </c>
       <c r="H96" t="n">
-        <v>4.7006</v>
+        <v>4.9772</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9316</v>
+        <v>0.9404</v>
       </c>
       <c r="F97" t="n">
-        <v>1.8017</v>
+        <v>0.101</v>
       </c>
       <c r="G97" t="n">
-        <v>2.2918</v>
+        <v>2.1963</v>
       </c>
       <c r="H97" t="n">
-        <v>4.694</v>
+        <v>4.9574</v>
       </c>
     </row>
     <row r="98">
@@ -3546,20 +3546,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9689</v>
+        <v>0.968</v>
       </c>
       <c r="F98" t="n">
-        <v>1.4842</v>
+        <v>0.4892</v>
       </c>
       <c r="G98" t="n">
-        <v>1.5053</v>
+        <v>1.5453</v>
       </c>
       <c r="H98" t="n">
-        <v>3.648</v>
+        <v>3.737</v>
       </c>
     </row>
     <row r="99">
@@ -3578,20 +3578,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9678</v>
+        <v>0.9457</v>
       </c>
       <c r="F99" t="n">
-        <v>1.4972</v>
+        <v>0.4979</v>
       </c>
       <c r="G99" t="n">
-        <v>1.5328</v>
+        <v>1.8737</v>
       </c>
       <c r="H99" t="n">
-        <v>3.6964</v>
+        <v>3.7048</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.975</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="F100" t="n">
-        <v>1.5069</v>
+        <v>0.4565</v>
       </c>
       <c r="G100" t="n">
-        <v>1.4188</v>
+        <v>1.4319</v>
       </c>
       <c r="H100" t="n">
-        <v>3.7323</v>
+        <v>3.8545</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9639</v>
+        <v>0.9729</v>
       </c>
       <c r="F101" t="n">
-        <v>1.5123</v>
+        <v>0.4584</v>
       </c>
       <c r="G101" t="n">
-        <v>1.6107</v>
+        <v>1.4656</v>
       </c>
       <c r="H101" t="n">
-        <v>3.7523</v>
+        <v>3.8477</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9729</v>
+        <v>0.9737</v>
       </c>
       <c r="F102" t="n">
-        <v>1.522</v>
+        <v>0.4591</v>
       </c>
       <c r="G102" t="n">
-        <v>1.4578</v>
+        <v>1.4793</v>
       </c>
       <c r="H102" t="n">
-        <v>3.7876</v>
+        <v>3.8452</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9677</v>
+        <v>0.95</v>
       </c>
       <c r="F103" t="n">
-        <v>1.4858</v>
+        <v>0.4653</v>
       </c>
       <c r="G103" t="n">
-        <v>1.5807</v>
+        <v>1.8341</v>
       </c>
       <c r="H103" t="n">
-        <v>3.654</v>
+        <v>3.8232</v>
       </c>
     </row>
     <row r="104">
@@ -3742,16 +3742,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9472</v>
+        <v>0.9494</v>
       </c>
       <c r="F104" t="n">
-        <v>1.4742</v>
+        <v>0.5041</v>
       </c>
       <c r="G104" t="n">
-        <v>1.8581</v>
+        <v>1.8143</v>
       </c>
       <c r="H104" t="n">
-        <v>3.6099</v>
+        <v>3.6817</v>
       </c>
     </row>
     <row r="105">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9442</v>
+        <v>0.9676</v>
       </c>
       <c r="F105" t="n">
-        <v>1.4683</v>
+        <v>0.523</v>
       </c>
       <c r="G105" t="n">
-        <v>1.8895</v>
+        <v>1.529</v>
       </c>
       <c r="H105" t="n">
-        <v>3.5873</v>
+        <v>3.611</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9764</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="F106" t="n">
-        <v>1.4958</v>
+        <v>0.4733</v>
       </c>
       <c r="G106" t="n">
-        <v>1.368</v>
+        <v>1.9112</v>
       </c>
       <c r="H106" t="n">
-        <v>3.6914</v>
+        <v>3.7947</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9605</v>
+        <v>0.9436</v>
       </c>
       <c r="F107" t="n">
-        <v>1.5062</v>
+        <v>0.4539</v>
       </c>
       <c r="G107" t="n">
-        <v>1.6608</v>
+        <v>1.9499</v>
       </c>
       <c r="H107" t="n">
-        <v>3.7299</v>
+        <v>3.8639</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9808</v>
+        <v>0.9666</v>
       </c>
       <c r="F108" t="n">
-        <v>1.4491</v>
+        <v>0.5667</v>
       </c>
       <c r="G108" t="n">
-        <v>1.3578</v>
+        <v>1.6264</v>
       </c>
       <c r="H108" t="n">
-        <v>3.5132</v>
+        <v>3.4419</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9808</v>
+        <v>0.965</v>
       </c>
       <c r="F109" t="n">
-        <v>1.439</v>
+        <v>0.555</v>
       </c>
       <c r="G109" t="n">
-        <v>1.303</v>
+        <v>1.6519</v>
       </c>
       <c r="H109" t="n">
-        <v>3.4733</v>
+        <v>3.4878</v>
       </c>
     </row>
     <row r="110">
@@ -3934,16 +3934,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9729</v>
       </c>
       <c r="F110" t="n">
-        <v>1.472</v>
+        <v>0.5218</v>
       </c>
       <c r="G110" t="n">
-        <v>1.4919</v>
+        <v>1.4924</v>
       </c>
       <c r="H110" t="n">
-        <v>3.6017</v>
+        <v>3.6156</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9748</v>
+        <v>0.9555</v>
       </c>
       <c r="F111" t="n">
-        <v>1.4507</v>
+        <v>0.5322</v>
       </c>
       <c r="G111" t="n">
-        <v>1.4108</v>
+        <v>1.7904</v>
       </c>
       <c r="H111" t="n">
-        <v>3.5195</v>
+        <v>3.5759</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9852</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>1.3219</v>
+        <v>0.6643</v>
       </c>
       <c r="G112" t="n">
-        <v>1.1332</v>
+        <v>1.1924</v>
       </c>
       <c r="H112" t="n">
-        <v>2.9745</v>
+        <v>3.0295</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9738</v>
       </c>
       <c r="F113" t="n">
-        <v>1.3343</v>
+        <v>0.6369</v>
       </c>
       <c r="G113" t="n">
-        <v>1.4009</v>
+        <v>1.4236</v>
       </c>
       <c r="H113" t="n">
-        <v>3.0312</v>
+        <v>3.1507</v>
       </c>
     </row>
     <row r="114">
@@ -4062,16 +4062,16 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9749</v>
+        <v>0.9745</v>
       </c>
       <c r="F114" t="n">
-        <v>1.4389</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="G114" t="n">
-        <v>1.4344</v>
+        <v>1.4531</v>
       </c>
       <c r="H114" t="n">
-        <v>3.4732</v>
+        <v>3.508</v>
       </c>
     </row>
     <row r="115">
@@ -4090,20 +4090,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9751</v>
+        <v>0.9552</v>
       </c>
       <c r="F115" t="n">
-        <v>1.4479</v>
+        <v>0.541</v>
       </c>
       <c r="G115" t="n">
-        <v>1.41</v>
+        <v>1.7848</v>
       </c>
       <c r="H115" t="n">
-        <v>3.5086</v>
+        <v>3.5424</v>
       </c>
     </row>
     <row r="116">
@@ -4126,16 +4126,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9862</v>
       </c>
       <c r="F116" t="n">
-        <v>1.1895</v>
+        <v>0.8089</v>
       </c>
       <c r="G116" t="n">
-        <v>0.9113</v>
+        <v>0.9475</v>
       </c>
       <c r="H116" t="n">
-        <v>2.2819</v>
+        <v>2.2858</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.9846</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="F117" t="n">
-        <v>1.1915</v>
+        <v>0.7992</v>
       </c>
       <c r="G117" t="n">
-        <v>0.9919</v>
+        <v>0.8448</v>
       </c>
       <c r="H117" t="n">
-        <v>2.2941</v>
+        <v>2.3428</v>
       </c>
     </row>
     <row r="118">
@@ -4186,20 +4186,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9442</v>
+        <v>0.9676</v>
       </c>
       <c r="F118" t="n">
-        <v>1.4683</v>
+        <v>0.523</v>
       </c>
       <c r="G118" t="n">
-        <v>1.8895</v>
+        <v>1.529</v>
       </c>
       <c r="H118" t="n">
-        <v>3.5873</v>
+        <v>3.611</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9738</v>
       </c>
       <c r="F119" t="n">
-        <v>1.3343</v>
+        <v>0.6369</v>
       </c>
       <c r="G119" t="n">
-        <v>1.4009</v>
+        <v>1.4236</v>
       </c>
       <c r="H119" t="n">
-        <v>3.0312</v>
+        <v>3.1507</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9534</v>
+        <v>0.9033</v>
       </c>
       <c r="F120" t="n">
-        <v>1.7672</v>
+        <v>0.256</v>
       </c>
       <c r="G120" t="n">
-        <v>1.9436</v>
+        <v>2.5082</v>
       </c>
       <c r="H120" t="n">
-        <v>4.5918</v>
+        <v>4.5098</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9534</v>
+        <v>0.9033</v>
       </c>
       <c r="F121" t="n">
-        <v>1.7672</v>
+        <v>0.256</v>
       </c>
       <c r="G121" t="n">
-        <v>1.9436</v>
+        <v>2.5082</v>
       </c>
       <c r="H121" t="n">
-        <v>4.5918</v>
+        <v>4.5098</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9186</v>
+        <v>0.9385</v>
       </c>
       <c r="F122" t="n">
-        <v>1.6359</v>
+        <v>0.3765</v>
       </c>
       <c r="G122" t="n">
-        <v>2.3893</v>
+        <v>2.1334</v>
       </c>
       <c r="H122" t="n">
-        <v>4.1805</v>
+        <v>4.1284</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9752</v>
+        <v>0.9738</v>
       </c>
       <c r="F123" t="n">
-        <v>1.3351</v>
+        <v>0.6372</v>
       </c>
       <c r="G123" t="n">
-        <v>1.3999</v>
+        <v>1.4244</v>
       </c>
       <c r="H123" t="n">
-        <v>3.0345</v>
+        <v>3.1494</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9809</v>
+        <v>0.9842</v>
       </c>
       <c r="F124" t="n">
-        <v>1.3878</v>
+        <v>0.5759</v>
       </c>
       <c r="G124" t="n">
-        <v>1.2889</v>
+        <v>1.2163</v>
       </c>
       <c r="H124" t="n">
-        <v>3.2645</v>
+        <v>3.405</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9328</v>
+        <v>0.9687</v>
       </c>
       <c r="F125" t="n">
-        <v>1.8014</v>
+        <v>0.095</v>
       </c>
       <c r="G125" t="n">
-        <v>2.3012</v>
+        <v>1.736</v>
       </c>
       <c r="H125" t="n">
-        <v>4.693</v>
+        <v>4.974</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.8752</v>
+        <v>0.9728</v>
       </c>
       <c r="F126" t="n">
-        <v>1.865</v>
+        <v>0.2085</v>
       </c>
       <c r="G126" t="n">
-        <v>2.9793</v>
+        <v>1.7187</v>
       </c>
       <c r="H126" t="n">
-        <v>4.8756</v>
+        <v>4.6516</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.9752</v>
+        <v>0.9558</v>
       </c>
       <c r="F127" t="n">
-        <v>1.3137</v>
+        <v>0.6945</v>
       </c>
       <c r="G127" t="n">
-        <v>1.2661</v>
+        <v>1.6217</v>
       </c>
       <c r="H127" t="n">
-        <v>2.9362</v>
+        <v>2.8897</v>
       </c>
     </row>
     <row r="128">
@@ -4506,20 +4506,20 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.8732</v>
+        <v>0.9737</v>
       </c>
       <c r="F128" t="n">
-        <v>1.8661</v>
+        <v>0.2036</v>
       </c>
       <c r="G128" t="n">
-        <v>2.9899</v>
+        <v>1.6867</v>
       </c>
       <c r="H128" t="n">
-        <v>4.8788</v>
+        <v>4.6661</v>
       </c>
     </row>
     <row r="129">
@@ -4542,16 +4542,16 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.8737</v>
+        <v>0.8883</v>
       </c>
       <c r="F129" t="n">
-        <v>1.8608</v>
+        <v>0.1956</v>
       </c>
       <c r="G129" t="n">
-        <v>2.9887</v>
+        <v>2.8597</v>
       </c>
       <c r="H129" t="n">
-        <v>4.8638</v>
+        <v>4.6894</v>
       </c>
     </row>
     <row r="130">
@@ -4574,16 +4574,16 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.8741</v>
+        <v>0.8891</v>
       </c>
       <c r="F130" t="n">
-        <v>1.8614</v>
+        <v>0.196</v>
       </c>
       <c r="G130" t="n">
-        <v>2.9871</v>
+        <v>2.8568</v>
       </c>
       <c r="H130" t="n">
-        <v>4.8654</v>
+        <v>4.6883</v>
       </c>
     </row>
     <row r="131">
@@ -4602,20 +4602,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.8744</v>
+        <v>0.9735</v>
       </c>
       <c r="F131" t="n">
-        <v>1.8626</v>
+        <v>0.2196</v>
       </c>
       <c r="G131" t="n">
-        <v>2.9833</v>
+        <v>1.6997</v>
       </c>
       <c r="H131" t="n">
-        <v>4.8688</v>
+        <v>4.619</v>
       </c>
     </row>
     <row r="132">
@@ -4634,20 +4634,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.8749</v>
+        <v>0.9742</v>
       </c>
       <c r="F132" t="n">
-        <v>1.8634</v>
+        <v>0.2128</v>
       </c>
       <c r="G132" t="n">
-        <v>2.9797</v>
+        <v>1.7017</v>
       </c>
       <c r="H132" t="n">
-        <v>4.8711</v>
+        <v>4.639</v>
       </c>
     </row>
     <row r="133">
@@ -4666,20 +4666,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.8751</v>
+        <v>0.9728</v>
       </c>
       <c r="F133" t="n">
-        <v>1.8649</v>
+        <v>0.2052</v>
       </c>
       <c r="G133" t="n">
-        <v>2.9802</v>
+        <v>1.7124</v>
       </c>
       <c r="H133" t="n">
-        <v>4.8753</v>
+        <v>4.6612</v>
       </c>
     </row>
     <row r="134">
@@ -4698,20 +4698,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.9735</v>
       </c>
       <c r="F134" t="n">
-        <v>1.8666</v>
+        <v>0.1963</v>
       </c>
       <c r="G134" t="n">
-        <v>2.9717</v>
+        <v>1.7044</v>
       </c>
       <c r="H134" t="n">
-        <v>4.8802</v>
+        <v>4.6874</v>
       </c>
     </row>
     <row r="135">
@@ -4730,20 +4730,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.8736</v>
+        <v>0.9729</v>
       </c>
       <c r="F135" t="n">
-        <v>1.8654</v>
+        <v>0.2023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.9873</v>
+        <v>1.6938</v>
       </c>
       <c r="H135" t="n">
-        <v>4.8769</v>
+        <v>4.6699</v>
       </c>
     </row>
     <row r="136">
@@ -4762,20 +4762,20 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.8744</v>
+        <v>0.9731</v>
       </c>
       <c r="F136" t="n">
-        <v>1.8616</v>
+        <v>0.2212</v>
       </c>
       <c r="G136" t="n">
-        <v>2.9842</v>
+        <v>1.6977</v>
       </c>
       <c r="H136" t="n">
-        <v>4.866</v>
+        <v>4.614</v>
       </c>
     </row>
     <row r="137">
@@ -4794,20 +4794,20 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9742</v>
+        <v>0.9653</v>
       </c>
       <c r="F137" t="n">
-        <v>1.7445</v>
+        <v>0.3026</v>
       </c>
       <c r="G137" t="n">
-        <v>1.6944</v>
+        <v>1.882</v>
       </c>
       <c r="H137" t="n">
-        <v>4.5232</v>
+        <v>4.3665</v>
       </c>
     </row>
     <row r="138">
@@ -4826,20 +4826,20 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9752</v>
+        <v>0.9784</v>
       </c>
       <c r="F138" t="n">
-        <v>1.6958</v>
+        <v>0.3011</v>
       </c>
       <c r="G138" t="n">
-        <v>1.6785</v>
+        <v>1.6709</v>
       </c>
       <c r="H138" t="n">
-        <v>4.3728</v>
+        <v>4.371</v>
       </c>
     </row>
     <row r="139">
@@ -4858,20 +4858,20 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9585</v>
+        <v>0.9628</v>
       </c>
       <c r="F139" t="n">
-        <v>1.7539</v>
+        <v>0.2884</v>
       </c>
       <c r="G139" t="n">
-        <v>1.9407</v>
+        <v>1.9703</v>
       </c>
       <c r="H139" t="n">
-        <v>4.5518</v>
+        <v>4.4107</v>
       </c>
     </row>
     <row r="140">
@@ -4894,16 +4894,16 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.976</v>
+        <v>0.9754</v>
       </c>
       <c r="F140" t="n">
-        <v>1.3247</v>
+        <v>0.6514</v>
       </c>
       <c r="G140" t="n">
-        <v>1.4086</v>
+        <v>1.4439</v>
       </c>
       <c r="H140" t="n">
-        <v>2.9874</v>
+        <v>3.087</v>
       </c>
     </row>
     <row r="141">
@@ -4926,16 +4926,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9872</v>
+        <v>0.9861</v>
       </c>
       <c r="F141" t="n">
-        <v>1.3299</v>
+        <v>0.6461</v>
       </c>
       <c r="G141" t="n">
-        <v>1.1503</v>
+        <v>1.184</v>
       </c>
       <c r="H141" t="n">
-        <v>3.0109</v>
+        <v>3.1105</v>
       </c>
     </row>
     <row r="142">
@@ -4954,20 +4954,20 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9752</v>
+        <v>0.9784</v>
       </c>
       <c r="F142" t="n">
-        <v>1.6958</v>
+        <v>0.3011</v>
       </c>
       <c r="G142" t="n">
-        <v>1.6785</v>
+        <v>1.6709</v>
       </c>
       <c r="H142" t="n">
-        <v>4.3728</v>
+        <v>4.371</v>
       </c>
     </row>
     <row r="143">
@@ -4990,16 +4990,16 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9627</v>
+        <v>0.9689</v>
       </c>
       <c r="F143" t="n">
-        <v>1.7448</v>
+        <v>0.3126</v>
       </c>
       <c r="G143" t="n">
-        <v>1.8719</v>
+        <v>1.793</v>
       </c>
       <c r="H143" t="n">
-        <v>4.5242</v>
+        <v>4.3349</v>
       </c>
     </row>
     <row r="144">
@@ -5018,20 +5018,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9636</v>
+        <v>0.9749</v>
       </c>
       <c r="F144" t="n">
-        <v>1.7219</v>
+        <v>0.341</v>
       </c>
       <c r="G144" t="n">
-        <v>1.8371</v>
+        <v>1.6275</v>
       </c>
       <c r="H144" t="n">
-        <v>4.4542</v>
+        <v>4.2446</v>
       </c>
     </row>
     <row r="145">
@@ -5054,16 +5054,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9872</v>
+        <v>0.9861</v>
       </c>
       <c r="F145" t="n">
-        <v>1.3299</v>
+        <v>0.6461</v>
       </c>
       <c r="G145" t="n">
-        <v>1.1503</v>
+        <v>1.184</v>
       </c>
       <c r="H145" t="n">
-        <v>3.0109</v>
+        <v>3.1105</v>
       </c>
     </row>
     <row r="146">
@@ -5082,20 +5082,20 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.9631</v>
+        <v>0.9564</v>
       </c>
       <c r="F146" t="n">
-        <v>1.3025</v>
+        <v>0.6944</v>
       </c>
       <c r="G146" t="n">
-        <v>1.5096</v>
+        <v>1.6127</v>
       </c>
       <c r="H146" t="n">
-        <v>2.8832</v>
+        <v>2.8904</v>
       </c>
     </row>
     <row r="147">
@@ -5114,20 +5114,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.9633</v>
+        <v>0.9571</v>
       </c>
       <c r="F147" t="n">
-        <v>1.3045</v>
+        <v>0.6954</v>
       </c>
       <c r="G147" t="n">
-        <v>1.5138</v>
+        <v>1.6076</v>
       </c>
       <c r="H147" t="n">
-        <v>2.8926</v>
+        <v>2.8854</v>
       </c>
     </row>
     <row r="148">
@@ -5146,20 +5146,20 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="F148" t="n">
-        <v>1.3047</v>
+        <v>0.6932</v>
       </c>
       <c r="G148" t="n">
-        <v>1.2381</v>
+        <v>1.606</v>
       </c>
       <c r="H148" t="n">
-        <v>2.8936</v>
+        <v>2.8959</v>
       </c>
     </row>
     <row r="149">
@@ -5178,20 +5178,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.9843</v>
+        <v>0.9738</v>
       </c>
       <c r="F149" t="n">
-        <v>1.3175</v>
+        <v>0.6918</v>
       </c>
       <c r="G149" t="n">
-        <v>1.0387</v>
+        <v>1.2934</v>
       </c>
       <c r="H149" t="n">
-        <v>2.9537</v>
+        <v>2.9024</v>
       </c>
     </row>
     <row r="150">
@@ -5210,20 +5210,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.9626</v>
+        <v>0.956</v>
       </c>
       <c r="F150" t="n">
-        <v>1.3113</v>
+        <v>0.6927</v>
       </c>
       <c r="G150" t="n">
-        <v>1.5198</v>
+        <v>1.6244</v>
       </c>
       <c r="H150" t="n">
-        <v>2.9247</v>
+        <v>2.8982</v>
       </c>
     </row>
     <row r="151">
@@ -5242,20 +5242,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.9631</v>
+        <v>0.956</v>
       </c>
       <c r="F151" t="n">
-        <v>1.3111</v>
+        <v>0.6925</v>
       </c>
       <c r="G151" t="n">
-        <v>1.509</v>
+        <v>1.6244</v>
       </c>
       <c r="H151" t="n">
-        <v>2.924</v>
+        <v>2.8994</v>
       </c>
     </row>
     <row r="152">
@@ -5274,20 +5274,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.963</v>
+        <v>0.9568</v>
       </c>
       <c r="F152" t="n">
-        <v>1.3108</v>
+        <v>0.6924</v>
       </c>
       <c r="G152" t="n">
-        <v>1.5154</v>
+        <v>1.6129</v>
       </c>
       <c r="H152" t="n">
-        <v>2.9225</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="153">
@@ -5306,20 +5306,20 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.963</v>
+        <v>0.9565</v>
       </c>
       <c r="F153" t="n">
-        <v>1.3052</v>
+        <v>0.6929</v>
       </c>
       <c r="G153" t="n">
-        <v>1.5135</v>
+        <v>1.6142</v>
       </c>
       <c r="H153" t="n">
-        <v>2.8959</v>
+        <v>2.8974</v>
       </c>
     </row>
     <row r="154">
@@ -5338,20 +5338,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.9732</v>
       </c>
       <c r="F154" t="n">
-        <v>1.3112</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="G154" t="n">
-        <v>1.4937</v>
+        <v>1.3052</v>
       </c>
       <c r="H154" t="n">
-        <v>2.9245</v>
+        <v>2.868</v>
       </c>
     </row>
     <row r="155">
@@ -5370,20 +5370,20 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.9771</v>
+        <v>0.9853</v>
       </c>
       <c r="F155" t="n">
-        <v>1.196</v>
+        <v>0.8045</v>
       </c>
       <c r="G155" t="n">
-        <v>1.1705</v>
+        <v>0.955</v>
       </c>
       <c r="H155" t="n">
-        <v>2.3212</v>
+        <v>2.3119</v>
       </c>
     </row>
     <row r="156">
@@ -5402,20 +5402,20 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.9767</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="F156" t="n">
-        <v>1.1885</v>
+        <v>0.8032</v>
       </c>
       <c r="G156" t="n">
-        <v>1.1714</v>
+        <v>1.0066</v>
       </c>
       <c r="H156" t="n">
-        <v>2.276</v>
+        <v>2.3193</v>
       </c>
     </row>
     <row r="157">
@@ -5438,16 +5438,16 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.9755</v>
+        <v>0.9748</v>
       </c>
       <c r="F157" t="n">
-        <v>1.1981</v>
+        <v>0.8108</v>
       </c>
       <c r="G157" t="n">
-        <v>1.2026</v>
+        <v>1.2206</v>
       </c>
       <c r="H157" t="n">
-        <v>2.3332</v>
+        <v>2.2744</v>
       </c>
     </row>
     <row r="158">
@@ -5466,20 +5466,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.9898</v>
+        <v>0.9911</v>
       </c>
       <c r="F158" t="n">
-        <v>1.1551</v>
+        <v>0.8451</v>
       </c>
       <c r="G158" t="n">
-        <v>0.8255</v>
+        <v>0.7657</v>
       </c>
       <c r="H158" t="n">
-        <v>2.0644</v>
+        <v>2.0579</v>
       </c>
     </row>
     <row r="159">
@@ -5498,20 +5498,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.9073</v>
+        <v>0.9745</v>
       </c>
       <c r="F159" t="n">
-        <v>1.8671</v>
+        <v>0.2037</v>
       </c>
       <c r="G159" t="n">
-        <v>2.6007</v>
+        <v>1.7512</v>
       </c>
       <c r="H159" t="n">
-        <v>4.8816</v>
+        <v>4.6657</v>
       </c>
     </row>
     <row r="160">
@@ -5530,20 +5530,20 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.9724</v>
       </c>
       <c r="F160" t="n">
-        <v>1.3977</v>
+        <v>0.6051</v>
       </c>
       <c r="G160" t="n">
-        <v>1.7756</v>
+        <v>1.4045</v>
       </c>
       <c r="H160" t="n">
-        <v>3.3058</v>
+        <v>3.2857</v>
       </c>
     </row>
     <row r="161">
@@ -5562,20 +5562,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.9516</v>
+        <v>0.972</v>
       </c>
       <c r="F161" t="n">
-        <v>1.3997</v>
+        <v>0.6039</v>
       </c>
       <c r="G161" t="n">
-        <v>1.7854</v>
+        <v>1.4118</v>
       </c>
       <c r="H161" t="n">
-        <v>3.3142</v>
+        <v>3.2907</v>
       </c>
     </row>
     <row r="162">
@@ -5594,20 +5594,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.907</v>
+        <v>0.9562</v>
       </c>
       <c r="F162" t="n">
-        <v>1.8679</v>
+        <v>0.2085</v>
       </c>
       <c r="G162" t="n">
-        <v>2.6082</v>
+        <v>2.1009</v>
       </c>
       <c r="H162" t="n">
-        <v>4.8839</v>
+        <v>4.6516</v>
       </c>
     </row>
     <row r="163">
@@ -5626,20 +5626,20 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9558</v>
+        <v>0.9732</v>
       </c>
       <c r="F163" t="n">
-        <v>1.6782</v>
+        <v>0.3072</v>
       </c>
       <c r="G163" t="n">
-        <v>2.2022</v>
+        <v>1.8216</v>
       </c>
       <c r="H163" t="n">
-        <v>4.3172</v>
+        <v>4.352</v>
       </c>
     </row>
     <row r="164">
@@ -5662,16 +5662,16 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9758</v>
+        <v>0.9755</v>
       </c>
       <c r="F164" t="n">
-        <v>1.3253</v>
+        <v>0.6514</v>
       </c>
       <c r="G164" t="n">
-        <v>1.4116</v>
+        <v>1.4436</v>
       </c>
       <c r="H164" t="n">
-        <v>2.9902</v>
+        <v>3.0869</v>
       </c>
     </row>
     <row r="165">
@@ -5690,20 +5690,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9328</v>
+        <v>0.9687</v>
       </c>
       <c r="F165" t="n">
-        <v>1.8014</v>
+        <v>0.095</v>
       </c>
       <c r="G165" t="n">
-        <v>2.3012</v>
+        <v>1.736</v>
       </c>
       <c r="H165" t="n">
-        <v>4.693</v>
+        <v>4.974</v>
       </c>
     </row>
     <row r="166">
@@ -5722,20 +5722,20 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.8195</v>
+        <v>0.8526</v>
       </c>
       <c r="F166" t="n">
-        <v>1.9543</v>
+        <v>0.0043</v>
       </c>
       <c r="G166" t="n">
-        <v>3.425</v>
+        <v>3.3073</v>
       </c>
       <c r="H166" t="n">
-        <v>5.1211</v>
+        <v>5.2172</v>
       </c>
     </row>
     <row r="167">
@@ -5754,20 +5754,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9779</v>
+        <v>0.9811</v>
       </c>
       <c r="F167" t="n">
-        <v>1.7305</v>
+        <v>0.2786</v>
       </c>
       <c r="G167" t="n">
-        <v>1.7255</v>
+        <v>1.5995</v>
       </c>
       <c r="H167" t="n">
-        <v>4.4806</v>
+        <v>4.441</v>
       </c>
     </row>
     <row r="168">
@@ -5786,20 +5786,20 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9862</v>
+        <v>0.9764</v>
       </c>
       <c r="F168" t="n">
-        <v>1.3011</v>
+        <v>0.6807</v>
       </c>
       <c r="G168" t="n">
-        <v>1.1082</v>
+        <v>1.4022</v>
       </c>
       <c r="H168" t="n">
-        <v>2.8764</v>
+        <v>2.9545</v>
       </c>
     </row>
     <row r="169">
@@ -5818,20 +5818,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9881</v>
       </c>
       <c r="F169" t="n">
-        <v>1.2044</v>
+        <v>0.7853</v>
       </c>
       <c r="G169" t="n">
-        <v>0.9214</v>
+        <v>0.8983</v>
       </c>
       <c r="H169" t="n">
-        <v>2.37</v>
+        <v>2.4225</v>
       </c>
     </row>
     <row r="170">
@@ -5850,20 +5850,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9758</v>
+        <v>0.977</v>
       </c>
       <c r="F170" t="n">
-        <v>1.4366</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="G170" t="n">
-        <v>1.6012</v>
+        <v>1.634</v>
       </c>
       <c r="H170" t="n">
-        <v>3.4639</v>
+        <v>3.6767</v>
       </c>
     </row>
     <row r="171">
@@ -5882,20 +5882,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9816</v>
+        <v>0.9817</v>
       </c>
       <c r="F171" t="n">
-        <v>1.2323</v>
+        <v>0.7245</v>
       </c>
       <c r="G171" t="n">
-        <v>1.2192</v>
+        <v>1.2372</v>
       </c>
       <c r="H171" t="n">
-        <v>2.5267</v>
+        <v>2.7444</v>
       </c>
     </row>
     <row r="172">
@@ -5918,16 +5918,16 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9725</v>
+        <v>0.9754</v>
       </c>
       <c r="F172" t="n">
-        <v>1.6738</v>
+        <v>0.355</v>
       </c>
       <c r="G172" t="n">
-        <v>1.7668</v>
+        <v>1.6802</v>
       </c>
       <c r="H172" t="n">
-        <v>4.3031</v>
+        <v>4.199</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C16.0/RANDOMSEARCH_DETAILS_C16.0.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/C16.0/RANDOMSEARCH_DETAILS_C16.0.xlsx
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -5210,11 +5210,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.956</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="F150" t="n">
         <v>0.6927</v>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E153" t="n">
